--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\GitHub\momentum_app_cloud\investment_os_v3\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D492E722-805D-43D3-B4CE-CE404FAE8E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AACA18B-C574-48E8-A371-4F4EE0D8556D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1263,23 +1263,23 @@
         <v/>
       </c>
       <c r="O2" s="12">
-        <f t="shared" ref="O2:O29" si="2">IFERROR(K2/H2-1,"")</f>
+        <f>IFERROR(K2/H2-1,"")</f>
         <v>9.0413448432530741E-2</v>
       </c>
       <c r="P2" s="12" t="str">
-        <f t="shared" ref="P2:P29" ca="1" si="3">IFERROR(L2/J2-1,"")</f>
+        <f t="shared" ref="P2:P29" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
         <v/>
       </c>
       <c r="Q2" s="11" t="str">
-        <f t="shared" ref="Q2:Q29" ca="1" si="4">IFERROR(N2-M2,"")</f>
+        <f t="shared" ref="Q2:Q29" ca="1" si="3">IFERROR(N2-M2,"")</f>
         <v/>
       </c>
       <c r="R2" s="12" t="str">
-        <f t="shared" ref="R2:R29" ca="1" si="5">IFERROR(N2/M2-1,"")</f>
+        <f t="shared" ref="R2:R29" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
         <v/>
       </c>
       <c r="S2" s="12">
-        <f t="shared" ref="S2:S29" ca="1" si="6">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ref="S2:S29" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1349,23 +1349,23 @@
         <v>30775</v>
       </c>
       <c r="O3" s="12">
+        <f t="shared" ref="O3:O29" si="6">IFERROR(K3/H3-1,"")</f>
+        <v>0.41014479472140764</v>
+      </c>
+      <c r="P3" s="12">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="11">
+        <f t="shared" si="3"/>
+        <v>8951</v>
+      </c>
+      <c r="R3" s="12">
+        <f t="shared" si="4"/>
         <v>0.41014479472140764</v>
       </c>
-      <c r="P3" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="11">
-        <f t="shared" si="4"/>
-        <v>8951</v>
-      </c>
-      <c r="R3" s="12">
-        <f t="shared" si="5"/>
-        <v>0.41014479472140764</v>
-      </c>
       <c r="S3" s="12">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="5"/>
         <v>4.2098745942994127E-2</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -1408,10 +1408,10 @@
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" s="8">
-        <v>1018.6</v>
+        <v>1078.93</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>48</v>
@@ -1433,23 +1433,23 @@
         <v/>
       </c>
       <c r="O4" s="12">
-        <f t="shared" si="2"/>
-        <v>0.36167288435107015</v>
+        <f t="shared" si="6"/>
+        <v>0.28553288906601915</v>
       </c>
       <c r="P4" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q4" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q4" s="11" t="str">
+      <c r="R4" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R4" s="12" t="str">
+      <c r="S4" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S4" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -1519,23 +1519,23 @@
         <v>55722.6</v>
       </c>
       <c r="O5" s="12">
+        <f t="shared" si="6"/>
+        <v>0.8195443645083933</v>
+      </c>
+      <c r="P5" s="12">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="11">
+        <f t="shared" si="3"/>
+        <v>25098.12</v>
+      </c>
+      <c r="R5" s="12">
+        <f t="shared" si="4"/>
         <v>0.8195443645083933</v>
       </c>
-      <c r="P5" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="11">
-        <f t="shared" si="4"/>
-        <v>25098.12</v>
-      </c>
-      <c r="R5" s="12">
-        <f t="shared" si="5"/>
-        <v>0.8195443645083933</v>
-      </c>
       <c r="S5" s="12">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="5"/>
         <v>7.6225884018946685E-2</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="8">
-        <v>38.296999999999997</v>
+        <v>39.1</v>
       </c>
       <c r="L6" s="13" t="str">
         <f ca="1">IF(I6="DKK",1,IFERROR(_xludf.XLOOKUP(I6,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1603,23 +1603,23 @@
         <v/>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="2"/>
-        <v>-5.7188577055637624E-2</v>
+        <f t="shared" si="6"/>
+        <v>-3.7419990152634086E-2</v>
       </c>
       <c r="P6" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q6" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q6" s="11" t="str">
+      <c r="R6" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R6" s="12" t="str">
+      <c r="S6" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S6" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="8">
-        <v>342.9</v>
+        <v>347.05</v>
       </c>
       <c r="L7" s="13" t="str">
         <f ca="1">IF(I7="DKK",1,IFERROR(_xludf.XLOOKUP(I7,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1687,23 +1687,23 @@
         <v/>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="2"/>
-        <v>-0.11641929499072357</v>
+        <f t="shared" si="6"/>
+        <v>-0.10572562358276638</v>
       </c>
       <c r="P7" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q7" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q7" s="11" t="str">
+      <c r="R7" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R7" s="12" t="str">
+      <c r="S7" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S7" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -1773,23 +1773,23 @@
         <v>54873</v>
       </c>
       <c r="O8" s="12">
+        <f t="shared" si="6"/>
+        <v>1.1470124235850916</v>
+      </c>
+      <c r="P8" s="12">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11">
+        <f t="shared" si="3"/>
+        <v>29315.16</v>
+      </c>
+      <c r="R8" s="12">
+        <f t="shared" si="4"/>
         <v>1.1470124235850916</v>
       </c>
-      <c r="P8" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="11">
-        <f t="shared" si="4"/>
-        <v>29315.16</v>
-      </c>
-      <c r="R8" s="12">
-        <f t="shared" si="5"/>
-        <v>1.1470124235850916</v>
-      </c>
       <c r="S8" s="12">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="5"/>
         <v>7.5063671360842132E-2</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -1859,23 +1859,23 @@
         <v>109502.39999999999</v>
       </c>
       <c r="O9" s="12">
+        <f t="shared" si="6"/>
+        <v>-0.23619574388300368</v>
+      </c>
+      <c r="P9" s="12">
         <f t="shared" si="2"/>
-        <v>-0.23619574388300368</v>
-      </c>
-      <c r="P9" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="11">
+        <v>-33862.080000000016</v>
+      </c>
+      <c r="R9" s="12">
         <f t="shared" si="4"/>
-        <v>-33862.080000000016</v>
-      </c>
-      <c r="R9" s="12">
-        <f t="shared" si="5"/>
         <v>-0.23619574388300379</v>
       </c>
       <c r="S9" s="12">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0.14979410943129551</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -1945,23 +1945,23 @@
         <v>29731.200000000001</v>
       </c>
       <c r="O10" s="12">
+        <f t="shared" si="6"/>
+        <v>0.23873909532781301</v>
+      </c>
+      <c r="P10" s="12">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <f t="shared" si="3"/>
+        <v>5730.02</v>
+      </c>
+      <c r="R10" s="12">
+        <f t="shared" si="4"/>
         <v>0.23873909532781301</v>
       </c>
-      <c r="P10" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="11">
-        <f t="shared" si="4"/>
-        <v>5730.02</v>
-      </c>
-      <c r="R10" s="12">
-        <f t="shared" si="5"/>
-        <v>0.23873909532781301</v>
-      </c>
       <c r="S10" s="12">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="5"/>
         <v>4.0670876860449942E-2</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -2004,17 +2004,17 @@
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H11" s="8">
-        <v>144.16999999999999</v>
+        <v>142.44</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="8">
-        <v>147.12</v>
+        <v>138.18</v>
       </c>
       <c r="L11" s="13" t="str">
         <f ca="1">IF(I11="DKK",1,IFERROR(_xludf.XLOOKUP(I11,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2029,23 +2029,23 @@
         <v/>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="2"/>
-        <v>2.0461954636887159E-2</v>
+        <f t="shared" si="6"/>
+        <v>-2.9907329401853366E-2</v>
       </c>
       <c r="P11" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q11" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q11" s="11" t="str">
+      <c r="R11" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R11" s="12" t="str">
+      <c r="S11" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S11" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="8">
-        <v>406.07499999999999</v>
+        <v>385</v>
       </c>
       <c r="L12" s="13" t="str">
         <f ca="1">IF(I12="DKK",1,IFERROR(_xludf.XLOOKUP(I12,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2113,23 +2113,23 @@
         <v/>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.9616127474649914E-2</v>
+        <f t="shared" si="6"/>
+        <v>-7.0497344278126484E-2</v>
       </c>
       <c r="P12" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q12" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q12" s="11" t="str">
+      <c r="R12" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R12" s="12" t="str">
+      <c r="S12" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S12" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="8">
-        <v>366.6</v>
+        <v>374.8</v>
       </c>
       <c r="L13" s="13" t="str">
         <f ca="1">IF(I13="DKK",1,IFERROR(_xludf.XLOOKUP(I13,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2197,23 +2197,23 @@
         <v/>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="2"/>
-        <v>5.4585152838448892E-4</v>
+        <f t="shared" si="6"/>
+        <v>2.2925764192139875E-2</v>
       </c>
       <c r="P13" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q13" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q13" s="11" t="str">
+      <c r="R13" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R13" s="12" t="str">
+      <c r="S13" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S13" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -2283,23 +2283,23 @@
         <v>18295.2</v>
       </c>
       <c r="O14" s="12">
+        <f t="shared" si="6"/>
+        <v>0.16154690071311029</v>
+      </c>
+      <c r="P14" s="12">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="11">
+        <f t="shared" si="3"/>
+        <v>2544.4799999999996</v>
+      </c>
+      <c r="R14" s="12">
+        <f t="shared" si="4"/>
         <v>0.16154690071311029</v>
       </c>
-      <c r="P14" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="11">
-        <f t="shared" si="4"/>
-        <v>2544.4799999999996</v>
-      </c>
-      <c r="R14" s="12">
-        <f t="shared" si="5"/>
-        <v>0.16154690071311029</v>
-      </c>
       <c r="S14" s="12">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="5"/>
         <v>2.5026969188505804E-2</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -2367,23 +2367,23 @@
         <v/>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-9.8486137098145909E-2</v>
       </c>
       <c r="P15" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q15" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q15" s="11" t="str">
+      <c r="R15" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R15" s="12" t="str">
+      <c r="S15" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S15" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T15" s="6" t="s">
@@ -2453,23 +2453,23 @@
         <v/>
       </c>
       <c r="O16" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>7.1589780626523325E-2</v>
       </c>
       <c r="P16" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q16" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q16" s="11" t="str">
+      <c r="R16" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R16" s="12" t="str">
+      <c r="S16" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S16" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -2537,23 +2537,23 @@
         <v/>
       </c>
       <c r="O17" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-0.27486187845303867</v>
       </c>
       <c r="P17" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q17" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q17" s="11" t="str">
+      <c r="R17" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R17" s="12" t="str">
+      <c r="S17" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S17" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -2621,23 +2621,23 @@
         <v/>
       </c>
       <c r="O18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-0.12445867068348704</v>
       </c>
       <c r="P18" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q18" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q18" s="11" t="str">
+      <c r="R18" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R18" s="12" t="str">
+      <c r="S18" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S18" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -2680,10 +2680,10 @@
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7">
-        <v>413</v>
+        <v>363</v>
       </c>
       <c r="H19" s="8">
-        <v>9.6199999999999992</v>
+        <v>9</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>48</v>
@@ -2705,23 +2705,23 @@
         <v/>
       </c>
       <c r="O19" s="12">
-        <f t="shared" si="2"/>
-        <v>0.66320166320166329</v>
+        <f t="shared" si="6"/>
+        <v>0.77777777777777768</v>
       </c>
       <c r="P19" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q19" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q19" s="11" t="str">
+      <c r="R19" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R19" s="12" t="str">
+      <c r="S19" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S19" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T19" s="6" t="s">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="8">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="L20" s="13" t="str">
         <f ca="1">IF(I20="DKK",1,IFERROR(_xludf.XLOOKUP(I20,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2789,23 +2789,23 @@
         <v/>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="2"/>
-        <v>-0.12402876689529518</v>
+        <f t="shared" si="6"/>
+        <v>-0.19410646554367161</v>
       </c>
       <c r="P20" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q20" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q20" s="11" t="str">
+      <c r="R20" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R20" s="12" t="str">
+      <c r="S20" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S20" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -2873,23 +2873,23 @@
         <v/>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-7.4288359176116536E-2</v>
       </c>
       <c r="P21" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q21" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q21" s="11" t="str">
+      <c r="R21" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R21" s="12" t="str">
+      <c r="S21" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S21" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -2957,23 +2957,23 @@
         <v/>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-6.8541300527240723E-2</v>
       </c>
       <c r="P22" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q22" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q22" s="11" t="str">
+      <c r="R22" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R22" s="12" t="str">
+      <c r="S22" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S22" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -3041,23 +3041,23 @@
         <v/>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-0.14199914199914199</v>
       </c>
       <c r="P23" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q23" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q23" s="11" t="str">
+      <c r="R23" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R23" s="12" t="str">
+      <c r="S23" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S23" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L24" s="13" t="str">
         <f ca="1">IF(I24="DKK",1,IFERROR(_xludf.XLOOKUP(I24,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3125,23 +3125,23 @@
         <v/>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="2"/>
-        <v>-0.27684705315174163</v>
+        <f t="shared" si="6"/>
+        <v>-0.33710979872242985</v>
       </c>
       <c r="P24" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q24" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q24" s="11" t="str">
+      <c r="R24" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R24" s="12" t="str">
+      <c r="S24" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S24" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -3209,23 +3209,23 @@
         <v/>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-9.8286744815148874E-2</v>
       </c>
       <c r="P25" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q25" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q25" s="11" t="str">
+      <c r="R25" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R25" s="12" t="str">
+      <c r="S25" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S25" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="8">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L26" s="13" t="str">
         <f ca="1">IF(I26="DKK",1,IFERROR(_xludf.XLOOKUP(I26,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3293,23 +3293,23 @@
         <v/>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="2"/>
-        <v>-0.27429533024821207</v>
+        <f t="shared" si="6"/>
+        <v>-0.28481278923012199</v>
       </c>
       <c r="P26" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q26" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q26" s="11" t="str">
+      <c r="R26" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R26" s="12" t="str">
+      <c r="S26" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S26" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -3377,23 +3377,23 @@
         <v/>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-2.0113460546673623E-2</v>
       </c>
       <c r="P27" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q27" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q27" s="11" t="str">
+      <c r="R27" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R27" s="12" t="str">
+      <c r="S27" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S27" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="8">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L28" s="13" t="str">
         <f ca="1">IF(I28="DKK",1,IFERROR(_xludf.XLOOKUP(I28,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3461,23 +3461,23 @@
         <v/>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="2"/>
-        <v>2.515723270440251E-2</v>
+        <f t="shared" si="6"/>
+        <v>3.1446540880503138E-2</v>
       </c>
       <c r="P28" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q28" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q28" s="11" t="str">
+      <c r="R28" s="12" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="R28" s="12" t="str">
+      <c r="S28" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="S28" s="12">
-        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -3547,23 +3547,23 @@
         <v>432120</v>
       </c>
       <c r="O29" s="12">
+        <f t="shared" si="6"/>
+        <v>1.7425742574257428</v>
+      </c>
+      <c r="P29" s="12">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="11">
+        <f t="shared" si="3"/>
+        <v>274560</v>
+      </c>
+      <c r="R29" s="12">
+        <f t="shared" si="4"/>
         <v>1.7425742574257428</v>
       </c>
-      <c r="P29" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="11">
-        <f t="shared" si="4"/>
-        <v>274560</v>
-      </c>
-      <c r="R29" s="12">
-        <f t="shared" si="5"/>
-        <v>1.7425742574257428</v>
-      </c>
       <c r="S29" s="12">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0.59111974319696581</v>
       </c>
       <c r="T29" s="6" t="s">

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AACA18B-C574-48E8-A371-4F4EE0D8556D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5647EB-196C-419E-B76F-99EDB56DEA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="8">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="L2" s="13" t="str">
         <f ca="1">IF(I2="DKK",1,IFERROR(_xludf.XLOOKUP(I2,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O2" s="12">
         <f>IFERROR(K2/H2-1,"")</f>
-        <v>9.0413448432530741E-2</v>
+        <v>9.5073334964293599E-2</v>
       </c>
       <c r="P2" s="12" t="str">
         <f t="shared" ref="P2:P29" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
@@ -1334,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="8">
-        <v>615.5</v>
+        <v>620</v>
       </c>
       <c r="L3" s="13">
         <f>IF(I3="DKK",1,IFERROR(_xludf.XLOOKUP(I3,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1346,11 +1346,11 @@
       </c>
       <c r="N3" s="11">
         <f t="shared" si="1"/>
-        <v>30775</v>
+        <v>31000</v>
       </c>
       <c r="O3" s="12">
         <f t="shared" ref="O3:O29" si="6">IFERROR(K3/H3-1,"")</f>
-        <v>0.41014479472140764</v>
+        <v>0.42045454545454541</v>
       </c>
       <c r="P3" s="12">
         <f t="shared" si="2"/>
@@ -1358,15 +1358,15 @@
       </c>
       <c r="Q3" s="11">
         <f t="shared" si="3"/>
-        <v>8951</v>
+        <v>9176</v>
       </c>
       <c r="R3" s="12">
         <f t="shared" si="4"/>
-        <v>0.41014479472140764</v>
+        <v>0.42045454545454541</v>
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.2098745942994127E-2</v>
+        <v>4.2012057731614504E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="8">
-        <v>1387</v>
+        <v>1474</v>
       </c>
       <c r="L4" s="13" t="str">
         <f ca="1">IF(I4="DKK",1,IFERROR(_xludf.XLOOKUP(I4,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="O4" s="12">
         <f t="shared" si="6"/>
-        <v>0.28553288906601915</v>
+        <v>0.36616833344146515</v>
       </c>
       <c r="P4" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1504,7 +1504,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="8">
-        <v>364.2</v>
+        <v>373.2</v>
       </c>
       <c r="L5" s="13">
         <f>IF(I5="DKK",1,IFERROR(_xludf.XLOOKUP(I5,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1516,11 +1516,11 @@
       </c>
       <c r="N5" s="11">
         <f t="shared" si="1"/>
-        <v>55722.6</v>
+        <v>57099.6</v>
       </c>
       <c r="O5" s="12">
         <f t="shared" si="6"/>
-        <v>0.8195443645083933</v>
+        <v>0.86450839328537166</v>
       </c>
       <c r="P5" s="12">
         <f t="shared" si="2"/>
@@ -1528,15 +1528,15 @@
       </c>
       <c r="Q5" s="11">
         <f t="shared" si="3"/>
-        <v>25098.12</v>
+        <v>26475.119999999999</v>
       </c>
       <c r="R5" s="12">
         <f t="shared" si="4"/>
-        <v>0.8195443645083933</v>
+        <v>0.86450839328537166</v>
       </c>
       <c r="S5" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.6225884018946685E-2</v>
+        <v>7.7382957795228885E-2</v>
       </c>
       <c r="T5" s="6" t="s">
         <v>43</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="8">
-        <v>39.1</v>
+        <v>38.909999999999997</v>
       </c>
       <c r="L6" s="13" t="str">
         <f ca="1">IF(I6="DKK",1,IFERROR(_xludf.XLOOKUP(I6,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="O6" s="12">
         <f t="shared" si="6"/>
-        <v>-3.7419990152634086E-2</v>
+        <v>-4.20974889217135E-2</v>
       </c>
       <c r="P6" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="8">
-        <v>347.05</v>
+        <v>387.95</v>
       </c>
       <c r="L7" s="13" t="str">
         <f ca="1">IF(I7="DKK",1,IFERROR(_xludf.XLOOKUP(I7,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="6"/>
-        <v>-0.10572562358276638</v>
+        <v>-3.349824778395849E-4</v>
       </c>
       <c r="P7" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1758,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="8">
-        <v>871</v>
+        <v>905</v>
       </c>
       <c r="L8" s="13">
         <f>IF(I8="DKK",1,IFERROR(_xludf.XLOOKUP(I8,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1770,11 +1770,11 @@
       </c>
       <c r="N8" s="11">
         <f t="shared" si="1"/>
-        <v>54873</v>
+        <v>57015</v>
       </c>
       <c r="O8" s="12">
         <f t="shared" si="6"/>
-        <v>1.1470124235850916</v>
+        <v>1.2308223230132125</v>
       </c>
       <c r="P8" s="12">
         <f t="shared" si="2"/>
@@ -1782,15 +1782,15 @@
       </c>
       <c r="Q8" s="11">
         <f t="shared" si="3"/>
-        <v>29315.16</v>
+        <v>31457.16</v>
       </c>
       <c r="R8" s="12">
         <f t="shared" si="4"/>
-        <v>1.1470124235850916</v>
+        <v>1.2308223230132125</v>
       </c>
       <c r="S8" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.5063671360842132E-2</v>
+        <v>7.7268305534451645E-2</v>
       </c>
       <c r="T8" s="6" t="s">
         <v>58</v>
@@ -1844,7 +1844,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="8">
-        <v>325.89999999999998</v>
+        <v>329.1</v>
       </c>
       <c r="L9" s="13">
         <f>IF(I9="DKK",1,IFERROR(_xludf.XLOOKUP(I9,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1856,11 +1856,11 @@
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
-        <v>109502.39999999999</v>
+        <v>110577.60000000001</v>
       </c>
       <c r="O9" s="12">
         <f t="shared" si="6"/>
-        <v>-0.23619574388300368</v>
+        <v>-0.22869597825067967</v>
       </c>
       <c r="P9" s="12">
         <f t="shared" si="2"/>
@@ -1868,15 +1868,15 @@
       </c>
       <c r="Q9" s="11">
         <f t="shared" si="3"/>
-        <v>-33862.080000000016</v>
+        <v>-32786.880000000005</v>
       </c>
       <c r="R9" s="12">
         <f t="shared" si="4"/>
-        <v>-0.23619574388300379</v>
+        <v>-0.22869597825067967</v>
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.14979410943129551</v>
+        <v>0.14985782306527021</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>69</v>
@@ -1930,7 +1930,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="8">
-        <v>782.4</v>
+        <v>795</v>
       </c>
       <c r="L10" s="13">
         <f>IF(I10="DKK",1,IFERROR(_xludf.XLOOKUP(I10,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>29731.200000000001</v>
+        <v>30210</v>
       </c>
       <c r="O10" s="12">
         <f t="shared" si="6"/>
-        <v>0.23873909532781301</v>
+        <v>0.2586881145010369</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" si="2"/>
@@ -1954,15 +1954,15 @@
       </c>
       <c r="Q10" s="11">
         <f t="shared" si="3"/>
-        <v>5730.02</v>
+        <v>6208.82</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="4"/>
-        <v>0.23873909532781301</v>
+        <v>0.25868811450103713</v>
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.0670876860449942E-2</v>
+        <v>4.0941427873292718E-2</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>74</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="8">
-        <v>138.18</v>
+        <v>149.12</v>
       </c>
       <c r="L11" s="13" t="str">
         <f ca="1">IF(I11="DKK",1,IFERROR(_xludf.XLOOKUP(I11,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="O11" s="12">
         <f t="shared" si="6"/>
-        <v>-2.9907329401853366E-2</v>
+        <v>4.6896939062061271E-2</v>
       </c>
       <c r="P11" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="8">
-        <v>385</v>
+        <v>392.49</v>
       </c>
       <c r="L12" s="13" t="str">
         <f ca="1">IF(I12="DKK",1,IFERROR(_xludf.XLOOKUP(I12,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="O12" s="12">
         <f t="shared" si="6"/>
-        <v>-7.0497344278126484E-2</v>
+        <v>-5.2414292612264601E-2</v>
       </c>
       <c r="P12" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="8">
-        <v>374.8</v>
+        <v>365.8</v>
       </c>
       <c r="L13" s="13" t="str">
         <f ca="1">IF(I13="DKK",1,IFERROR(_xludf.XLOOKUP(I13,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="O13" s="12">
         <f t="shared" si="6"/>
-        <v>2.2925764192139875E-2</v>
+        <v>-1.6375545851528006E-3</v>
       </c>
       <c r="P13" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2268,7 +2268,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="8">
-        <v>169.4</v>
+        <v>183.9</v>
       </c>
       <c r="L14" s="13">
         <f>IF(I14="DKK",1,IFERROR(_xludf.XLOOKUP(I14,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2280,11 +2280,11 @@
       </c>
       <c r="N14" s="11">
         <f t="shared" si="1"/>
-        <v>18295.2</v>
+        <v>19861.2</v>
       </c>
       <c r="O14" s="12">
         <f t="shared" si="6"/>
-        <v>0.16154690071311029</v>
+        <v>0.26097092704333513</v>
       </c>
       <c r="P14" s="12">
         <f t="shared" si="2"/>
@@ -2292,15 +2292,15 @@
       </c>
       <c r="Q14" s="11">
         <f t="shared" si="3"/>
-        <v>2544.4799999999996</v>
+        <v>4110.4799999999996</v>
       </c>
       <c r="R14" s="12">
         <f t="shared" si="4"/>
-        <v>0.16154690071311029</v>
+        <v>0.26097092704333513</v>
       </c>
       <c r="S14" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.5026969188505804E-2</v>
+        <v>2.6916447774811034E-2</v>
       </c>
       <c r="T14" s="6" t="s">
         <v>91</v>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="8">
-        <v>47.48</v>
+        <v>45</v>
       </c>
       <c r="L16" s="13" t="str">
         <f ca="1">IF(I16="DKK",1,IFERROR(_xludf.XLOOKUP(I16,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O16" s="12">
         <f t="shared" si="6"/>
-        <v>7.1589780626523325E-2</v>
+        <v>1.5617947097589679E-2</v>
       </c>
       <c r="P16" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L19" s="13" t="str">
         <f ca="1">IF(I19="DKK",1,IFERROR(_xludf.XLOOKUP(I19,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="O19" s="12">
         <f t="shared" si="6"/>
-        <v>0.77777777777777768</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="P19" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="8">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L20" s="13" t="str">
         <f ca="1">IF(I20="DKK",1,IFERROR(_xludf.XLOOKUP(I20,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="O20" s="12">
         <f t="shared" si="6"/>
-        <v>-0.19410646554367161</v>
+        <v>-0.1503079038884364</v>
       </c>
       <c r="P20" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="8">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L22" s="13" t="str">
         <f ca="1">IF(I22="DKK",1,IFERROR(_xludf.XLOOKUP(I22,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="O22" s="12">
         <f t="shared" si="6"/>
-        <v>-6.8541300527240723E-2</v>
+        <v>-0.1036906854130053</v>
       </c>
       <c r="P22" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="8">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L26" s="13" t="str">
         <f ca="1">IF(I26="DKK",1,IFERROR(_xludf.XLOOKUP(I26,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O26" s="12">
         <f t="shared" si="6"/>
-        <v>-0.28481278923012199</v>
+        <v>-0.29533024821203191</v>
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="8">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L27" s="13" t="str">
         <f ca="1">IF(I27="DKK",1,IFERROR(_xludf.XLOOKUP(I27,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O27" s="12">
         <f t="shared" si="6"/>
-        <v>-2.0113460546673623E-2</v>
+        <v>-3.3006704486848948E-2</v>
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="8">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L28" s="13" t="str">
         <f ca="1">IF(I28="DKK",1,IFERROR(_xludf.XLOOKUP(I28,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="O28" s="12">
         <f t="shared" si="6"/>
-        <v>3.1446540880503138E-2</v>
+        <v>1.8867924528301883E-2</v>
       </c>
       <c r="P28" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="S29" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.59111974319696581</v>
+        <v>0.58562098022533093</v>
       </c>
       <c r="T29" s="6" t="s">
         <v>58</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5647EB-196C-419E-B76F-99EDB56DEA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E49755FE-FE10-4E64-81C1-7528381B392D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30960" yWindow="2160" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="8">
-        <v>940</v>
+        <v>946.6</v>
       </c>
       <c r="L2" s="13" t="str">
         <f ca="1">IF(I2="DKK",1,IFERROR(_xludf.XLOOKUP(I2,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O2" s="12">
         <f>IFERROR(K2/H2-1,"")</f>
-        <v>9.5073334964293599E-2</v>
+        <v>0.10276214774170245</v>
       </c>
       <c r="P2" s="12" t="str">
         <f t="shared" ref="P2:P29" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
@@ -1334,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="8">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="L3" s="13">
         <f>IF(I3="DKK",1,IFERROR(_xludf.XLOOKUP(I3,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1346,11 +1346,11 @@
       </c>
       <c r="N3" s="11">
         <f t="shared" si="1"/>
-        <v>31000</v>
+        <v>31300</v>
       </c>
       <c r="O3" s="12">
         <f t="shared" ref="O3:O29" si="6">IFERROR(K3/H3-1,"")</f>
-        <v>0.42045454545454541</v>
+        <v>0.43420087976539579</v>
       </c>
       <c r="P3" s="12">
         <f t="shared" si="2"/>
@@ -1358,15 +1358,15 @@
       </c>
       <c r="Q3" s="11">
         <f t="shared" si="3"/>
-        <v>9176</v>
+        <v>9476</v>
       </c>
       <c r="R3" s="12">
         <f t="shared" si="4"/>
-        <v>0.42045454545454541</v>
+        <v>0.43420087976539579</v>
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.2012057731614504E-2</v>
+        <v>4.2994003504079968E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="8">
-        <v>1474</v>
+        <v>1440</v>
       </c>
       <c r="L4" s="13" t="str">
         <f ca="1">IF(I4="DKK",1,IFERROR(_xludf.XLOOKUP(I4,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="O4" s="12">
         <f t="shared" si="6"/>
-        <v>0.36616833344146515</v>
+        <v>0.33465563104186558</v>
       </c>
       <c r="P4" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1504,7 +1504,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="8">
-        <v>373.2</v>
+        <v>373.5</v>
       </c>
       <c r="L5" s="13">
         <f>IF(I5="DKK",1,IFERROR(_xludf.XLOOKUP(I5,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1516,11 +1516,11 @@
       </c>
       <c r="N5" s="11">
         <f t="shared" si="1"/>
-        <v>57099.6</v>
+        <v>57145.5</v>
       </c>
       <c r="O5" s="12">
         <f t="shared" si="6"/>
-        <v>0.86450839328537166</v>
+        <v>0.86600719424460437</v>
       </c>
       <c r="P5" s="12">
         <f t="shared" si="2"/>
@@ -1528,15 +1528,15 @@
       </c>
       <c r="Q5" s="11">
         <f t="shared" si="3"/>
-        <v>26475.119999999999</v>
+        <v>26521.02</v>
       </c>
       <c r="R5" s="12">
         <f t="shared" si="4"/>
-        <v>0.86450839328537166</v>
+        <v>0.86600719424460437</v>
       </c>
       <c r="S5" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.7382957795228885E-2</v>
+        <v>7.8495649432664585E-2</v>
       </c>
       <c r="T5" s="6" t="s">
         <v>43</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="8">
-        <v>38.909999999999997</v>
+        <v>39.76</v>
       </c>
       <c r="L6" s="13" t="str">
         <f ca="1">IF(I6="DKK",1,IFERROR(_xludf.XLOOKUP(I6,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="O6" s="12">
         <f t="shared" si="6"/>
-        <v>-4.20974889217135E-2</v>
+        <v>-2.1171836533727229E-2</v>
       </c>
       <c r="P6" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="8">
-        <v>387.95</v>
+        <v>404.9</v>
       </c>
       <c r="L7" s="13" t="str">
         <f ca="1">IF(I7="DKK",1,IFERROR(_xludf.XLOOKUP(I7,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="6"/>
-        <v>-3.349824778395849E-4</v>
+        <v>4.3341579055864665E-2</v>
       </c>
       <c r="P7" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1758,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="8">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="L8" s="13">
         <f>IF(I8="DKK",1,IFERROR(_xludf.XLOOKUP(I8,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1770,11 +1770,11 @@
       </c>
       <c r="N8" s="11">
         <f t="shared" si="1"/>
-        <v>57015</v>
+        <v>55818</v>
       </c>
       <c r="O8" s="12">
         <f t="shared" si="6"/>
-        <v>1.2308223230132125</v>
+        <v>1.1839873792151447</v>
       </c>
       <c r="P8" s="12">
         <f t="shared" si="2"/>
@@ -1782,15 +1782,15 @@
       </c>
       <c r="Q8" s="11">
         <f t="shared" si="3"/>
-        <v>31457.16</v>
+        <v>30260.16</v>
       </c>
       <c r="R8" s="12">
         <f t="shared" si="4"/>
-        <v>1.2308223230132125</v>
+        <v>1.1839873792151447</v>
       </c>
       <c r="S8" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.7268305534451645E-2</v>
+        <v>7.667218171216407E-2</v>
       </c>
       <c r="T8" s="6" t="s">
         <v>58</v>
@@ -1844,7 +1844,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="8">
-        <v>329.1</v>
+        <v>303.85000000000002</v>
       </c>
       <c r="L9" s="13">
         <f>IF(I9="DKK",1,IFERROR(_xludf.XLOOKUP(I9,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1856,11 +1856,11 @@
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
-        <v>110577.60000000001</v>
+        <v>102093.6</v>
       </c>
       <c r="O9" s="12">
         <f t="shared" si="6"/>
-        <v>-0.22869597825067967</v>
+        <v>-0.28787381644323606</v>
       </c>
       <c r="P9" s="12">
         <f t="shared" si="2"/>
@@ -1868,15 +1868,15 @@
       </c>
       <c r="Q9" s="11">
         <f t="shared" si="3"/>
-        <v>-32786.880000000005</v>
+        <v>-41270.880000000005</v>
       </c>
       <c r="R9" s="12">
         <f t="shared" si="4"/>
-        <v>-0.22869597825067967</v>
+        <v>-0.28787381644323617</v>
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.14985782306527021</v>
+        <v>0.14023682415795971</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>69</v>
@@ -1930,7 +1930,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="8">
-        <v>795</v>
+        <v>812.2</v>
       </c>
       <c r="L10" s="13">
         <f>IF(I10="DKK",1,IFERROR(_xludf.XLOOKUP(I10,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>30210</v>
+        <v>30863.600000000002</v>
       </c>
       <c r="O10" s="12">
         <f t="shared" si="6"/>
-        <v>0.2586881145010369</v>
+        <v>0.2859201089279777</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" si="2"/>
@@ -1954,15 +1954,15 @@
       </c>
       <c r="Q10" s="11">
         <f t="shared" si="3"/>
-        <v>6208.82</v>
+        <v>6862.4200000000019</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="4"/>
-        <v>0.25868811450103713</v>
+        <v>0.2859201089279777</v>
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.0941427873292718E-2</v>
+        <v>4.2394559953626919E-2</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>74</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="8">
-        <v>149.12</v>
+        <v>150.76</v>
       </c>
       <c r="L11" s="13" t="str">
         <f ca="1">IF(I11="DKK",1,IFERROR(_xludf.XLOOKUP(I11,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="O11" s="12">
         <f t="shared" si="6"/>
-        <v>4.6896939062061271E-2</v>
+        <v>5.8410558831788695E-2</v>
       </c>
       <c r="P11" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="8">
-        <v>392.49</v>
+        <v>400.26</v>
       </c>
       <c r="L12" s="13" t="str">
         <f ca="1">IF(I12="DKK",1,IFERROR(_xludf.XLOOKUP(I12,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="O12" s="12">
         <f t="shared" si="6"/>
-        <v>-5.2414292612264601E-2</v>
+        <v>-3.3655239014968585E-2</v>
       </c>
       <c r="P12" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="8">
-        <v>365.8</v>
+        <v>359.2</v>
       </c>
       <c r="L13" s="13" t="str">
         <f ca="1">IF(I13="DKK",1,IFERROR(_xludf.XLOOKUP(I13,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="O13" s="12">
         <f t="shared" si="6"/>
-        <v>-1.6375545851528006E-3</v>
+        <v>-1.9650655021834051E-2</v>
       </c>
       <c r="P13" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2268,7 +2268,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="8">
-        <v>183.9</v>
+        <v>172.85</v>
       </c>
       <c r="L14" s="13">
         <f>IF(I14="DKK",1,IFERROR(_xludf.XLOOKUP(I14,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2280,11 +2280,11 @@
       </c>
       <c r="N14" s="11">
         <f t="shared" si="1"/>
-        <v>19861.2</v>
+        <v>18667.8</v>
       </c>
       <c r="O14" s="12">
         <f t="shared" si="6"/>
-        <v>0.26097092704333513</v>
+        <v>0.18520296215030174</v>
       </c>
       <c r="P14" s="12">
         <f t="shared" si="2"/>
@@ -2292,15 +2292,15 @@
       </c>
       <c r="Q14" s="11">
         <f t="shared" si="3"/>
-        <v>4110.4799999999996</v>
+        <v>2917.0799999999981</v>
       </c>
       <c r="R14" s="12">
         <f t="shared" si="4"/>
-        <v>0.26097092704333513</v>
+        <v>0.18520296215030152</v>
       </c>
       <c r="S14" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.6916447774811034E-2</v>
+        <v>2.5642283022794376E-2</v>
       </c>
       <c r="T14" s="6" t="s">
         <v>91</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="J15" s="9"/>
       <c r="K15" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L15" s="13" t="str">
         <f ca="1">IF(I15="DKK",1,IFERROR(_xludf.XLOOKUP(I15,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="O15" s="12">
         <f t="shared" si="6"/>
-        <v>-9.8486137098145909E-2</v>
+        <v>-8.1476441571695868E-2</v>
       </c>
       <c r="P15" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="8">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L16" s="13" t="str">
         <f ca="1">IF(I16="DKK",1,IFERROR(_xludf.XLOOKUP(I16,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O16" s="12">
         <f t="shared" si="6"/>
-        <v>1.5617947097589679E-2</v>
+        <v>3.8187234810869386E-2</v>
       </c>
       <c r="P16" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L19" s="13" t="str">
         <f ca="1">IF(I19="DKK",1,IFERROR(_xludf.XLOOKUP(I19,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="O19" s="12">
         <f t="shared" si="6"/>
-        <v>0.88888888888888884</v>
+        <v>0.77777777777777768</v>
       </c>
       <c r="P19" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L20" s="13" t="str">
         <f ca="1">IF(I20="DKK",1,IFERROR(_xludf.XLOOKUP(I20,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="O20" s="12">
         <f t="shared" si="6"/>
-        <v>-0.1503079038884364</v>
+        <v>-0.14154819155738929</v>
       </c>
       <c r="P20" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="8">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L22" s="13" t="str">
         <f ca="1">IF(I22="DKK",1,IFERROR(_xludf.XLOOKUP(I22,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="O22" s="12">
         <f t="shared" si="6"/>
-        <v>-0.1036906854130053</v>
+        <v>-6.8541300527240723E-2</v>
       </c>
       <c r="P22" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L23" s="13" t="str">
         <f ca="1">IF(I23="DKK",1,IFERROR(_xludf.XLOOKUP(I23,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="O23" s="12">
         <f t="shared" si="6"/>
-        <v>-0.14199914199914199</v>
+        <v>-0.10624910624910633</v>
       </c>
       <c r="P23" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="8">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="L26" s="13" t="str">
         <f ca="1">IF(I26="DKK",1,IFERROR(_xludf.XLOOKUP(I26,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O26" s="12">
         <f t="shared" si="6"/>
-        <v>-0.29533024821203191</v>
+        <v>-0.25326041228439211</v>
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L27" s="13" t="str">
         <f ca="1">IF(I27="DKK",1,IFERROR(_xludf.XLOOKUP(I27,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O27" s="12">
         <f t="shared" si="6"/>
-        <v>-3.3006704486848948E-2</v>
+        <v>-2.0113460546673623E-2</v>
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="8">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L28" s="13" t="str">
         <f ca="1">IF(I28="DKK",1,IFERROR(_xludf.XLOOKUP(I28,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="O28" s="12">
         <f t="shared" si="6"/>
-        <v>1.8867924528301883E-2</v>
+        <v>3.7735849056603765E-2</v>
       </c>
       <c r="P28" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="S29" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.58562098022533093</v>
+        <v>0.59356449821671042</v>
       </c>
       <c r="T29" s="6" t="s">
         <v>58</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E49755FE-FE10-4E64-81C1-7528381B392D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89796E9B-1BF5-4236-907D-405D652C6B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="wN/gCBMOd4DBG8tW9S4xTdQiSwCKOJbrXtIvltQJ2dBEiFa2se/+jpIXl8PdufpcYkat1fvM16So/lOtfDGZOQ==" workbookSaltValue="eJkq3fCOu/9W2lKjHkgUDQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="30960" yWindow="2160" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1248,7 +1249,7 @@
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="8">
-        <v>946.6</v>
+        <v>950.6</v>
       </c>
       <c r="L2" s="13" t="str">
         <f ca="1">IF(I2="DKK",1,IFERROR(_xludf.XLOOKUP(I2,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1264,7 +1265,7 @@
       </c>
       <c r="O2" s="12">
         <f>IFERROR(K2/H2-1,"")</f>
-        <v>0.10276214774170245</v>
+        <v>0.10742203427346553</v>
       </c>
       <c r="P2" s="12" t="str">
         <f t="shared" ref="P2:P29" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
@@ -1334,7 +1335,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="8">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="L3" s="13">
         <f>IF(I3="DKK",1,IFERROR(_xludf.XLOOKUP(I3,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1346,11 +1347,11 @@
       </c>
       <c r="N3" s="11">
         <f t="shared" si="1"/>
-        <v>31300</v>
+        <v>31500</v>
       </c>
       <c r="O3" s="12">
         <f t="shared" ref="O3:O29" si="6">IFERROR(K3/H3-1,"")</f>
-        <v>0.43420087976539579</v>
+        <v>0.44336510263929618</v>
       </c>
       <c r="P3" s="12">
         <f t="shared" si="2"/>
@@ -1358,15 +1359,15 @@
       </c>
       <c r="Q3" s="11">
         <f t="shared" si="3"/>
-        <v>9476</v>
+        <v>9676</v>
       </c>
       <c r="R3" s="12">
         <f t="shared" si="4"/>
-        <v>0.43420087976539579</v>
+        <v>0.44336510263929618</v>
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.2994003504079968E-2</v>
+        <v>4.305303122041812E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1418,7 +1419,7 @@
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="8">
-        <v>1440</v>
+        <v>1453.2</v>
       </c>
       <c r="L4" s="13" t="str">
         <f ca="1">IF(I4="DKK",1,IFERROR(_xludf.XLOOKUP(I4,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1434,7 +1435,7 @@
       </c>
       <c r="O4" s="12">
         <f t="shared" si="6"/>
-        <v>0.33465563104186558</v>
+        <v>0.346889974326416</v>
       </c>
       <c r="P4" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1504,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="8">
-        <v>373.5</v>
+        <v>375</v>
       </c>
       <c r="L5" s="13">
         <f>IF(I5="DKK",1,IFERROR(_xludf.XLOOKUP(I5,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1516,11 +1517,11 @@
       </c>
       <c r="N5" s="11">
         <f t="shared" si="1"/>
-        <v>57145.5</v>
+        <v>57375</v>
       </c>
       <c r="O5" s="12">
         <f t="shared" si="6"/>
-        <v>0.86600719424460437</v>
+        <v>0.87350119904076751</v>
       </c>
       <c r="P5" s="12">
         <f t="shared" si="2"/>
@@ -1528,15 +1529,15 @@
       </c>
       <c r="Q5" s="11">
         <f t="shared" si="3"/>
-        <v>26521.02</v>
+        <v>26750.52</v>
       </c>
       <c r="R5" s="12">
         <f t="shared" si="4"/>
-        <v>0.86600719424460437</v>
+        <v>0.87350119904076751</v>
       </c>
       <c r="S5" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.8495649432664585E-2</v>
+        <v>7.8418021151475864E-2</v>
       </c>
       <c r="T5" s="6" t="s">
         <v>43</v>
@@ -1588,7 +1589,7 @@
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="8">
-        <v>39.76</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="L6" s="13" t="str">
         <f ca="1">IF(I6="DKK",1,IFERROR(_xludf.XLOOKUP(I6,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1604,7 +1605,7 @@
       </c>
       <c r="O6" s="12">
         <f t="shared" si="6"/>
-        <v>-2.1171836533727229E-2</v>
+        <v>-1.4032496307237796E-2</v>
       </c>
       <c r="P6" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1672,7 +1673,7 @@
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="8">
-        <v>404.9</v>
+        <v>422.4</v>
       </c>
       <c r="L7" s="13" t="str">
         <f ca="1">IF(I7="DKK",1,IFERROR(_xludf.XLOOKUP(I7,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1688,7 +1689,7 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="6"/>
-        <v>4.3341579055864665E-2</v>
+        <v>8.843537414965974E-2</v>
       </c>
       <c r="P7" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1758,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="8">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="L8" s="13">
         <f>IF(I8="DKK",1,IFERROR(_xludf.XLOOKUP(I8,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1770,11 +1771,11 @@
       </c>
       <c r="N8" s="11">
         <f t="shared" si="1"/>
-        <v>55818</v>
+        <v>56574</v>
       </c>
       <c r="O8" s="12">
         <f t="shared" si="6"/>
-        <v>1.1839873792151447</v>
+        <v>1.2135673437191876</v>
       </c>
       <c r="P8" s="12">
         <f t="shared" si="2"/>
@@ -1782,15 +1783,15 @@
       </c>
       <c r="Q8" s="11">
         <f t="shared" si="3"/>
-        <v>30260.16</v>
+        <v>31016.16</v>
       </c>
       <c r="R8" s="12">
         <f t="shared" si="4"/>
-        <v>1.1839873792151447</v>
+        <v>1.2135673437191876</v>
       </c>
       <c r="S8" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>7.667218171216407E-2</v>
+        <v>7.7323244071870953E-2</v>
       </c>
       <c r="T8" s="6" t="s">
         <v>58</v>
@@ -1844,7 +1845,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="8">
-        <v>303.85000000000002</v>
+        <v>306.95</v>
       </c>
       <c r="L9" s="13">
         <f>IF(I9="DKK",1,IFERROR(_xludf.XLOOKUP(I9,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1856,11 +1857,11 @@
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
-        <v>102093.6</v>
+        <v>103135.2</v>
       </c>
       <c r="O9" s="12">
         <f t="shared" si="6"/>
-        <v>-0.28787381644323606</v>
+        <v>-0.28060841848692231</v>
       </c>
       <c r="P9" s="12">
         <f t="shared" si="2"/>
@@ -1868,15 +1869,15 @@
       </c>
       <c r="Q9" s="11">
         <f t="shared" si="3"/>
-        <v>-41270.880000000005</v>
+        <v>-40229.280000000013</v>
       </c>
       <c r="R9" s="12">
         <f t="shared" si="4"/>
-        <v>-0.28787381644323617</v>
+        <v>-0.28060841848692231</v>
       </c>
       <c r="S9" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.14023682415795971</v>
+        <v>0.14096136461981165</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>69</v>
@@ -1930,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="8">
-        <v>812.2</v>
+        <v>833.8</v>
       </c>
       <c r="L10" s="13">
         <f>IF(I10="DKK",1,IFERROR(_xludf.XLOOKUP(I10,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -1942,11 +1943,11 @@
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>30863.600000000002</v>
+        <v>31684.399999999998</v>
       </c>
       <c r="O10" s="12">
         <f t="shared" si="6"/>
-        <v>0.2859201089279777</v>
+        <v>0.32011842751064723</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" si="2"/>
@@ -1954,15 +1955,15 @@
       </c>
       <c r="Q10" s="11">
         <f t="shared" si="3"/>
-        <v>6862.4200000000019</v>
+        <v>7683.2199999999975</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="4"/>
-        <v>0.2859201089279777</v>
+        <v>0.32011842751064723</v>
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>4.2394559953626919E-2</v>
+        <v>4.3305062298419551E-2</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>74</v>
@@ -2014,7 +2015,7 @@
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="8">
-        <v>150.76</v>
+        <v>149.69999999999999</v>
       </c>
       <c r="L11" s="13" t="str">
         <f ca="1">IF(I11="DKK",1,IFERROR(_xludf.XLOOKUP(I11,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2030,7 +2031,7 @@
       </c>
       <c r="O11" s="12">
         <f t="shared" si="6"/>
-        <v>5.8410558831788695E-2</v>
+        <v>5.0968828980623382E-2</v>
       </c>
       <c r="P11" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2098,7 +2099,7 @@
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="8">
-        <v>400.26</v>
+        <v>417.42</v>
       </c>
       <c r="L12" s="13" t="str">
         <f ca="1">IF(I12="DKK",1,IFERROR(_xludf.XLOOKUP(I12,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2114,7 +2115,7 @@
       </c>
       <c r="O12" s="12">
         <f t="shared" si="6"/>
-        <v>-3.3655239014968585E-2</v>
+        <v>7.7740222114921487E-3</v>
       </c>
       <c r="P12" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2182,7 +2183,7 @@
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="8">
-        <v>359.2</v>
+        <v>360.6</v>
       </c>
       <c r="L13" s="13" t="str">
         <f ca="1">IF(I13="DKK",1,IFERROR(_xludf.XLOOKUP(I13,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2198,7 +2199,7 @@
       </c>
       <c r="O13" s="12">
         <f t="shared" si="6"/>
-        <v>-1.9650655021834051E-2</v>
+        <v>-1.5829694323143961E-2</v>
       </c>
       <c r="P13" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2268,7 +2269,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="8">
-        <v>172.85</v>
+        <v>178.4</v>
       </c>
       <c r="L14" s="13">
         <f>IF(I14="DKK",1,IFERROR(_xludf.XLOOKUP(I14,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2280,11 +2281,11 @@
       </c>
       <c r="N14" s="11">
         <f t="shared" si="1"/>
-        <v>18667.8</v>
+        <v>19267.2</v>
       </c>
       <c r="O14" s="12">
         <f t="shared" si="6"/>
-        <v>0.18520296215030174</v>
+        <v>0.22325836533187049</v>
       </c>
       <c r="P14" s="12">
         <f t="shared" si="2"/>
@@ -2292,15 +2293,15 @@
       </c>
       <c r="Q14" s="11">
         <f t="shared" si="3"/>
-        <v>2917.0799999999981</v>
+        <v>3516.4799999999996</v>
       </c>
       <c r="R14" s="12">
         <f t="shared" si="4"/>
-        <v>0.18520296215030152</v>
+        <v>0.22325836533187049</v>
       </c>
       <c r="S14" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.5642283022794376E-2</v>
+        <v>2.633369406762032E-2</v>
       </c>
       <c r="T14" s="6" t="s">
         <v>91</v>
@@ -2352,7 +2353,7 @@
       </c>
       <c r="J15" s="9"/>
       <c r="K15" s="8">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L15" s="13" t="str">
         <f ca="1">IF(I15="DKK",1,IFERROR(_xludf.XLOOKUP(I15,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2368,7 +2369,7 @@
       </c>
       <c r="O15" s="12">
         <f t="shared" si="6"/>
-        <v>-8.1476441571695868E-2</v>
+        <v>-3.0447354992345632E-2</v>
       </c>
       <c r="P15" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2438,7 +2439,7 @@
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L16" s="13" t="str">
         <f ca="1">IF(I16="DKK",1,IFERROR(_xludf.XLOOKUP(I16,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2454,7 +2455,7 @@
       </c>
       <c r="O16" s="12">
         <f t="shared" si="6"/>
-        <v>3.8187234810869386E-2</v>
+        <v>6.0756522524149092E-2</v>
       </c>
       <c r="P16" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2522,7 +2523,7 @@
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L17" s="13" t="str">
         <f ca="1">IF(I17="DKK",1,IFERROR(_xludf.XLOOKUP(I17,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2538,7 +2539,7 @@
       </c>
       <c r="O17" s="12">
         <f t="shared" si="6"/>
-        <v>-0.27486187845303867</v>
+        <v>-0.24033149171270718</v>
       </c>
       <c r="P17" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2690,7 +2691,7 @@
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L19" s="13" t="str">
         <f ca="1">IF(I19="DKK",1,IFERROR(_xludf.XLOOKUP(I19,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2706,7 +2707,7 @@
       </c>
       <c r="O19" s="12">
         <f t="shared" si="6"/>
-        <v>0.77777777777777768</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="P19" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2774,7 +2775,7 @@
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="8">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="L20" s="13" t="str">
         <f ca="1">IF(I20="DKK",1,IFERROR(_xludf.XLOOKUP(I20,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2790,7 +2791,7 @@
       </c>
       <c r="O20" s="12">
         <f t="shared" si="6"/>
-        <v>-0.14154819155738929</v>
+        <v>-7.1470492909012862E-2</v>
       </c>
       <c r="P20" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2942,7 +2943,7 @@
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="8">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L22" s="13" t="str">
         <f ca="1">IF(I22="DKK",1,IFERROR(_xludf.XLOOKUP(I22,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2958,7 +2959,7 @@
       </c>
       <c r="O22" s="12">
         <f t="shared" si="6"/>
-        <v>-6.8541300527240723E-2</v>
+        <v>-3.3391915641476255E-2</v>
       </c>
       <c r="P22" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3110,7 +3111,7 @@
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L24" s="13" t="str">
         <f ca="1">IF(I24="DKK",1,IFERROR(_xludf.XLOOKUP(I24,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3126,7 +3127,7 @@
       </c>
       <c r="O24" s="12">
         <f t="shared" si="6"/>
-        <v>-0.33710979872242985</v>
+        <v>-0.27684705315174163</v>
       </c>
       <c r="P24" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3194,7 +3195,7 @@
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L25" s="13" t="str">
         <f ca="1">IF(I25="DKK",1,IFERROR(_xludf.XLOOKUP(I25,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3210,7 +3211,7 @@
       </c>
       <c r="O25" s="12">
         <f t="shared" si="6"/>
-        <v>-9.8286744815148874E-2</v>
+        <v>-6.2218214607754785E-2</v>
       </c>
       <c r="P25" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3278,7 +3279,7 @@
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="8">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L26" s="13" t="str">
         <f ca="1">IF(I26="DKK",1,IFERROR(_xludf.XLOOKUP(I26,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3294,7 +3295,7 @@
       </c>
       <c r="O26" s="12">
         <f t="shared" si="6"/>
-        <v>-0.25326041228439211</v>
+        <v>-0.22170803533866212</v>
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3362,7 +3363,7 @@
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="8">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L27" s="13" t="str">
         <f ca="1">IF(I27="DKK",1,IFERROR(_xludf.XLOOKUP(I27,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3378,7 +3379,7 @@
       </c>
       <c r="O27" s="12">
         <f t="shared" si="6"/>
-        <v>-2.0113460546673623E-2</v>
+        <v>5.6730273336771386E-3</v>
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3446,7 +3447,7 @@
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L28" s="13" t="str">
         <f ca="1">IF(I28="DKK",1,IFERROR(_xludf.XLOOKUP(I28,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3462,7 +3463,7 @@
       </c>
       <c r="O28" s="12">
         <f t="shared" si="6"/>
-        <v>3.7735849056603765E-2</v>
+        <v>5.031446540880502E-2</v>
       </c>
       <c r="P28" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3564,7 +3565,7 @@
       </c>
       <c r="S29" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.59356449821671042</v>
+        <v>0.59060558257038343</v>
       </c>
       <c r="T29" s="6" t="s">
         <v>58</v>
@@ -3589,6 +3590,7 @@
       <c r="AB29" s="14"/>
     </row>
   </sheetData>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <conditionalFormatting sqref="G2:S29">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>0</formula>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:8001_{3A928361-D560-4955-9521-41211EBEC004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7153426-6C98-46F1-87E0-A6F000B5C204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50355" yWindow="4140" windowWidth="19380" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25215" yWindow="3975" windowWidth="19380" windowHeight="10005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="213">
   <si>
     <t>Asset_ID</t>
   </si>
@@ -666,6 +666,18 @@
   </si>
   <si>
     <t>Amount_DKK</t>
+  </si>
+  <si>
+    <t>A029</t>
+  </si>
+  <si>
+    <t>iShares Edge MSCI World Quality Factor UCITS ETF</t>
+  </si>
+  <si>
+    <t>IS3Q:XETR</t>
+  </si>
+  <si>
+    <t>IS3Q:DE</t>
   </si>
 </sst>
 </file>
@@ -679,7 +691,7 @@
     <numFmt numFmtId="167" formatCode="#,##0\ &quot;kr&quot;;[Red]\(#,##0\ &quot;kr&quot;\);\-"/>
     <numFmt numFmtId="168" formatCode="0.0%;[Red]\(0.0%\);\-"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -703,6 +715,10 @@
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -829,7 +845,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB30">
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Asset_ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Asset_Type"/>
@@ -1101,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB29"/>
+  <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1255,11 +1271,11 @@
         <v/>
       </c>
       <c r="M2" s="11">
-        <f t="shared" ref="M2:M29" si="0">IFERROR(G2*H2*J2,"")</f>
+        <f t="shared" ref="M2:M30" si="0">IFERROR(G2*H2*J2,"")</f>
         <v>0</v>
       </c>
       <c r="N2" s="11" t="str">
-        <f t="shared" ref="N2:N29" ca="1" si="1">IFERROR(G2*K2*L2,"")</f>
+        <f t="shared" ref="N2:N30" ca="1" si="1">IFERROR(G2*K2*L2,"")</f>
         <v/>
       </c>
       <c r="O2" s="12">
@@ -1267,19 +1283,19 @@
         <v>0.13468237048427878</v>
       </c>
       <c r="P2" s="12" t="str">
-        <f t="shared" ref="P2:P29" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
+        <f t="shared" ref="P2:P30" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
         <v/>
       </c>
       <c r="Q2" s="11" t="str">
-        <f t="shared" ref="Q2:Q29" ca="1" si="3">IFERROR(N2-M2,"")</f>
+        <f t="shared" ref="Q2:Q30" ca="1" si="3">IFERROR(N2-M2,"")</f>
         <v/>
       </c>
       <c r="R2" s="12" t="str">
-        <f t="shared" ref="R2:R29" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
+        <f t="shared" ref="R2:R30" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
         <v/>
       </c>
       <c r="S2" s="12">
-        <f t="shared" ref="S2:S29" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ref="S2:S30" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1349,7 +1365,7 @@
         <v>31875</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" ref="O3:O29" si="6">IFERROR(K3/H3-1,"")</f>
+        <f t="shared" ref="O3:O30" si="6">IFERROR(K3/H3-1,"")</f>
         <v>0.46054802052785915</v>
       </c>
       <c r="P3" s="12">
@@ -2502,62 +2518,41 @@
         <v>93</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>102</v>
+        <v>210</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>103</v>
+        <v>211</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>103</v>
+        <v>212</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="7">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="H17" s="8">
-        <v>28.96</v>
+        <v>78.83</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="8">
-        <v>23</v>
-      </c>
-      <c r="L17" s="13" t="str">
-        <f ca="1">IF(I17="DKK",1,IFERROR(_xludf.XLOOKUP(I17,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
-      </c>
-      <c r="M17" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
       <c r="O17" s="12">
         <f t="shared" si="6"/>
-        <v>-0.20580110497237569</v>
-      </c>
-      <c r="P17" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q17" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R17" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S17" s="12">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
+        <v>-1.0528986426487363E-2</v>
+      </c>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
       <c r="T17" s="6" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="U17" s="6" t="s">
         <v>35</v>
@@ -2586,27 +2581,27 @@
         <v>93</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="7">
-        <v>185</v>
+        <v>52</v>
       </c>
       <c r="H18" s="8">
-        <v>10.622</v>
+        <v>28.96</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="8">
-        <v>9.3000000000000007</v>
+        <v>23</v>
       </c>
       <c r="L18" s="13" t="str">
         <f ca="1">IF(I18="DKK",1,IFERROR(_xludf.XLOOKUP(I18,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2622,7 +2617,7 @@
       </c>
       <c r="O18" s="12">
         <f t="shared" si="6"/>
-        <v>-0.12445867068348704</v>
+        <v>-0.20580110497237569</v>
       </c>
       <c r="P18" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2670,27 +2665,27 @@
         <v>93</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7">
-        <v>363</v>
+        <v>185</v>
       </c>
       <c r="H19" s="8">
-        <v>9</v>
+        <v>10.622</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="8">
-        <v>17</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="L19" s="13" t="str">
         <f ca="1">IF(I19="DKK",1,IFERROR(_xludf.XLOOKUP(I19,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2706,7 +2701,7 @@
       </c>
       <c r="O19" s="12">
         <f t="shared" si="6"/>
-        <v>0.88888888888888884</v>
+        <v>-0.12445867068348704</v>
       </c>
       <c r="P19" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2725,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="U19" s="6" t="s">
         <v>35</v>
@@ -2754,27 +2749,27 @@
         <v>93</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="7">
-        <v>19</v>
+        <v>363</v>
       </c>
       <c r="H20" s="8">
-        <v>114.15900000000001</v>
+        <v>9</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="8">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="L20" s="13" t="str">
         <f ca="1">IF(I20="DKK",1,IFERROR(_xludf.XLOOKUP(I20,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2790,7 +2785,7 @@
       </c>
       <c r="O20" s="12">
         <f t="shared" si="6"/>
-        <v>-8.0230205240059971E-2</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="P20" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2838,27 +2833,27 @@
         <v>93</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="7">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="H21" s="8">
-        <v>8.6419999999999995</v>
+        <v>114.15900000000001</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="8">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="L21" s="13" t="str">
         <f ca="1">IF(I21="DKK",1,IFERROR(_xludf.XLOOKUP(I21,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2874,7 +2869,7 @@
       </c>
       <c r="O21" s="12">
         <f t="shared" si="6"/>
-        <v>-7.4288359176116536E-2</v>
+        <v>-8.0230205240059971E-2</v>
       </c>
       <c r="P21" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2893,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="U21" s="6" t="s">
         <v>35</v>
@@ -2922,27 +2917,27 @@
         <v>93</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="H22" s="8">
-        <v>56.9</v>
+        <v>8.6419999999999995</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="8">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="L22" s="13" t="str">
         <f ca="1">IF(I22="DKK",1,IFERROR(_xludf.XLOOKUP(I22,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2958,7 +2953,7 @@
       </c>
       <c r="O22" s="12">
         <f t="shared" si="6"/>
-        <v>-1.5817223198594021E-2</v>
+        <v>-7.4288359176116536E-2</v>
       </c>
       <c r="P22" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2977,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="U22" s="6" t="s">
         <v>35</v>
@@ -3006,27 +3001,27 @@
         <v>93</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H23" s="8">
-        <v>27.972000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="8">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="L23" s="13" t="str">
         <f ca="1">IF(I23="DKK",1,IFERROR(_xludf.XLOOKUP(I23,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3042,7 +3037,7 @@
       </c>
       <c r="O23" s="12">
         <f t="shared" si="6"/>
-        <v>-7.049907049907056E-2</v>
+        <v>-1.5817223198594021E-2</v>
       </c>
       <c r="P23" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3061,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="U23" s="6" t="s">
         <v>35</v>
@@ -3090,27 +3085,27 @@
         <v>93</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="7">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="H24" s="8">
-        <v>16.594000000000001</v>
+        <v>27.972000000000001</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="8">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L24" s="13" t="str">
         <f ca="1">IF(I24="DKK",1,IFERROR(_xludf.XLOOKUP(I24,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3126,7 +3121,7 @@
       </c>
       <c r="O24" s="12">
         <f t="shared" si="6"/>
-        <v>-0.27684705315174163</v>
+        <v>-7.049907049907056E-2</v>
       </c>
       <c r="P24" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3145,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="U24" s="6" t="s">
         <v>35</v>
@@ -3174,27 +3169,27 @@
         <v>93</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="H25" s="8">
-        <v>55.45</v>
+        <v>16.594000000000001</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="8">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="L25" s="13" t="str">
         <f ca="1">IF(I25="DKK",1,IFERROR(_xludf.XLOOKUP(I25,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3210,7 +3205,7 @@
       </c>
       <c r="O25" s="12">
         <f t="shared" si="6"/>
-        <v>-2.6149684400360695E-2</v>
+        <v>-0.27684705315174163</v>
       </c>
       <c r="P25" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3258,27 +3253,27 @@
         <v>93</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H26" s="8">
-        <v>95.08</v>
+        <v>55.45</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="8">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L26" s="13" t="str">
         <f ca="1">IF(I26="DKK",1,IFERROR(_xludf.XLOOKUP(I26,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3294,7 +3289,7 @@
       </c>
       <c r="O26" s="12">
         <f t="shared" si="6"/>
-        <v>-0.2111905763567522</v>
+        <v>-2.6149684400360695E-2</v>
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3313,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="U26" s="6" t="s">
         <v>35</v>
@@ -3342,27 +3337,27 @@
         <v>93</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H27" s="8">
-        <v>77.56</v>
+        <v>95.08</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="8">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L27" s="13" t="str">
         <f ca="1">IF(I27="DKK",1,IFERROR(_xludf.XLOOKUP(I27,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3378,7 +3373,7 @@
       </c>
       <c r="O27" s="12">
         <f t="shared" si="6"/>
-        <v>5.6730273336771386E-3</v>
+        <v>-0.2111905763567522</v>
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3397,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="U27" s="6" t="s">
         <v>35</v>
@@ -3426,27 +3421,27 @@
         <v>93</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H28" s="8">
-        <v>159</v>
+        <v>77.56</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="8">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="L28" s="13" t="str">
         <f ca="1">IF(I28="DKK",1,IFERROR(_xludf.XLOOKUP(I28,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3462,7 +3457,7 @@
       </c>
       <c r="O28" s="12">
         <f t="shared" si="6"/>
-        <v>5.6603773584905648E-2</v>
+        <v>5.6730273336771386E-3</v>
       </c>
       <c r="P28" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3481,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="U28" s="6" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="V28" s="10" t="b">
         <v>1</v>
@@ -3507,73 +3502,71 @@
         <v>142</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7">
-        <v>260</v>
+        <v>18</v>
       </c>
       <c r="H29" s="8">
-        <v>606</v>
+        <v>159</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J29" s="9">
-        <v>1</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="J29" s="9"/>
       <c r="K29" s="8">
-        <v>1662</v>
-      </c>
-      <c r="L29" s="13">
-        <f>IF(I29="DKK",1,IFERROR(_xludf.XLOOKUP(I29,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
+        <v>168</v>
+      </c>
+      <c r="L29" s="13" t="str">
+        <f ca="1">IF(I29="DKK",1,IFERROR(_xludf.XLOOKUP(I29,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v/>
       </c>
       <c r="M29" s="11">
         <f t="shared" si="0"/>
-        <v>157560</v>
-      </c>
-      <c r="N29" s="11">
-        <f t="shared" si="1"/>
-        <v>432120</v>
+        <v>0</v>
+      </c>
+      <c r="N29" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="O29" s="12">
         <f t="shared" si="6"/>
-        <v>1.7425742574257428</v>
-      </c>
-      <c r="P29" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="11">
-        <f t="shared" si="3"/>
-        <v>274560</v>
-      </c>
-      <c r="R29" s="12">
-        <f t="shared" si="4"/>
-        <v>1.7425742574257428</v>
+        <v>5.6603773584905648E-2</v>
+      </c>
+      <c r="P29" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q29" s="11" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R29" s="12" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="S29" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0.5915878216036613</v>
+        <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="U29" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="V29" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="10" t="b">
         <v>1</v>
@@ -3588,9 +3581,96 @@
       <c r="AA29" s="14"/>
       <c r="AB29" s="14"/>
     </row>
+    <row r="30" spans="1:28">
+      <c r="A30" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F30" s="6"/>
+      <c r="G30" s="7">
+        <v>260</v>
+      </c>
+      <c r="H30" s="8">
+        <v>606</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="9">
+        <v>1</v>
+      </c>
+      <c r="K30" s="8">
+        <v>1662</v>
+      </c>
+      <c r="L30" s="13">
+        <f>IF(I30="DKK",1,IFERROR(_xludf.XLOOKUP(I30,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
+      </c>
+      <c r="M30" s="11">
+        <f t="shared" si="0"/>
+        <v>157560</v>
+      </c>
+      <c r="N30" s="11">
+        <f t="shared" si="1"/>
+        <v>432120</v>
+      </c>
+      <c r="O30" s="12">
+        <f t="shared" si="6"/>
+        <v>1.7425742574257428</v>
+      </c>
+      <c r="P30" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="11">
+        <f t="shared" si="3"/>
+        <v>274560</v>
+      </c>
+      <c r="R30" s="12">
+        <f t="shared" si="4"/>
+        <v>1.7425742574257428</v>
+      </c>
+      <c r="S30" s="12">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.5915878216036613</v>
+      </c>
+      <c r="T30" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="U30" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="V30" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z30" s="6"/>
+      <c r="AA30" s="14"/>
+      <c r="AB30" s="14"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <conditionalFormatting sqref="G2:S29">
+  <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="G2:S30">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7153426-6C98-46F1-87E0-A6F000B5C204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA628DA-A48F-42D5-9B8F-D67AB518203E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25215" yWindow="3975" windowWidth="19380" windowHeight="10005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -2538,14 +2538,14 @@
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="12">
         <f t="shared" si="6"/>
-        <v>-1.0528986426487363E-2</v>
+        <v>2.1565393885576434E-3</v>
       </c>
       <c r="P17" s="12"/>
       <c r="Q17" s="11"/>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA628DA-A48F-42D5-9B8F-D67AB518203E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD5C251-1E50-4022-B15A-3C17CD01AA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="211">
   <si>
     <t>Asset_ID</t>
   </si>
@@ -293,9 +293,6 @@
     <t>A012</t>
   </si>
   <si>
-    <t>UNITED HEALTH GROUP INCORPORATED</t>
-  </si>
-  <si>
     <t>UNH:XETR</t>
   </si>
   <si>
@@ -666,9 +663,6 @@
   </si>
   <si>
     <t>Amount_DKK</t>
-  </si>
-  <si>
-    <t>A029</t>
   </si>
   <si>
     <t>iShares Edge MSCI World Quality Factor UCITS ETF</t>
@@ -845,7 +839,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB29">
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Asset_ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Asset_Type"/>
@@ -1117,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB30"/>
+  <dimension ref="A1:AB29"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1271,11 +1265,11 @@
         <v/>
       </c>
       <c r="M2" s="11">
-        <f t="shared" ref="M2:M30" si="0">IFERROR(G2*H2*J2,"")</f>
+        <f t="shared" ref="M2:M29" si="0">IFERROR(G2*H2*J2,"")</f>
         <v>0</v>
       </c>
       <c r="N2" s="11" t="str">
-        <f t="shared" ref="N2:N30" ca="1" si="1">IFERROR(G2*K2*L2,"")</f>
+        <f t="shared" ref="N2:N29" ca="1" si="1">IFERROR(G2*K2*L2,"")</f>
         <v/>
       </c>
       <c r="O2" s="12">
@@ -1283,19 +1277,19 @@
         <v>0.13468237048427878</v>
       </c>
       <c r="P2" s="12" t="str">
-        <f t="shared" ref="P2:P30" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
+        <f t="shared" ref="P2:P29" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
         <v/>
       </c>
       <c r="Q2" s="11" t="str">
-        <f t="shared" ref="Q2:Q30" ca="1" si="3">IFERROR(N2-M2,"")</f>
+        <f t="shared" ref="Q2:Q29" ca="1" si="3">IFERROR(N2-M2,"")</f>
         <v/>
       </c>
       <c r="R2" s="12" t="str">
-        <f t="shared" ref="R2:R30" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
+        <f t="shared" ref="R2:R29" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
         <v/>
       </c>
       <c r="S2" s="12">
-        <f t="shared" ref="S2:S30" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f ca="1">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1365,7 +1359,7 @@
         <v>31875</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" ref="O3:O30" si="6">IFERROR(K3/H3-1,"")</f>
+        <f t="shared" ref="O3:O29" si="5">IFERROR(K3/H3-1,"")</f>
         <v>0.46054802052785915</v>
       </c>
       <c r="P3" s="12">
@@ -1381,7 +1375,7 @@
         <v>0.46054802052785915</v>
       </c>
       <c r="S3" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W3=TRUE,IFERROR(N3/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>4.3638021414460576E-2</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -1449,7 +1443,7 @@
         <v/>
       </c>
       <c r="O4" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.38822722512118468</v>
       </c>
       <c r="P4" s="12" t="str">
@@ -1465,7 +1459,7 @@
         <v/>
       </c>
       <c r="S4" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W4=TRUE,IFERROR(N4/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -1535,7 +1529,7 @@
         <v>57742.2</v>
       </c>
       <c r="O5" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.88549160671462812</v>
       </c>
       <c r="P5" s="12">
@@ -1551,7 +1545,7 @@
         <v>0.88549160671462812</v>
       </c>
       <c r="S5" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W5=TRUE,IFERROR(N5/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>7.9051148552723619E-2</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -1619,7 +1613,7 @@
         <v/>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-1.5263417035942806E-2</v>
       </c>
       <c r="P6" s="12" t="str">
@@ -1635,7 +1629,7 @@
         <v/>
       </c>
       <c r="S6" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W6=TRUE,IFERROR(N6/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -1703,7 +1697,7 @@
         <v/>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>9.5135023706452326E-2</v>
       </c>
       <c r="P7" s="12" t="str">
@@ -1719,7 +1713,7 @@
         <v/>
       </c>
       <c r="S7" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W7=TRUE,IFERROR(N7/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -1789,7 +1783,7 @@
         <v>57330</v>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.2431473082232301</v>
       </c>
       <c r="P8" s="12">
@@ -1805,7 +1799,7 @@
         <v>1.2431473082232301</v>
       </c>
       <c r="S8" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W8=TRUE,IFERROR(N8/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>7.8486831927561562E-2</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -1875,7 +1869,7 @@
         <v>100128</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.32731376975169302</v>
       </c>
       <c r="P9" s="12">
@@ -1891,7 +1885,7 @@
         <v>-0.32731376975169302</v>
       </c>
       <c r="S9" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W9=TRUE,IFERROR(N9/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0.13707883319802694</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -1961,7 +1955,7 @@
         <v>32178.399999999998</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.34070074887984658</v>
       </c>
       <c r="P10" s="12">
@@ -1977,7 +1971,7 @@
         <v>0.34070074887984658</v>
       </c>
       <c r="S10" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W10=TRUE,IFERROR(N10/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>4.4053386926527945E-2</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -2045,7 +2039,7 @@
         <v/>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.10727323785453535</v>
       </c>
       <c r="P11" s="12" t="str">
@@ -2061,7 +2055,7 @@
         <v/>
       </c>
       <c r="S11" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W11=TRUE,IFERROR(N11/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -2129,7 +2123,7 @@
         <v/>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>9.1743119266054496E-3</v>
       </c>
       <c r="P12" s="12" t="str">
@@ -2145,7 +2139,7 @@
         <v/>
       </c>
       <c r="S12" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W12=TRUE,IFERROR(N12/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -2178,62 +2172,64 @@
         <v>29</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="7">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="H13" s="8">
-        <v>366.4</v>
+        <v>145.84</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" s="9"/>
+        <v>42</v>
+      </c>
+      <c r="J13" s="9">
+        <v>1</v>
+      </c>
       <c r="K13" s="8">
-        <v>354</v>
-      </c>
-      <c r="L13" s="13" t="str">
-        <f ca="1">IF(I13="DKK",1,IFERROR(_xludf.XLOOKUP(I13,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
+        <v>176.55</v>
+      </c>
+      <c r="L13" s="13">
+        <f>IF(I13="DKK",1,IFERROR(_xludf.XLOOKUP(I13,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
       </c>
       <c r="M13" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N13" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>15750.720000000001</v>
+      </c>
+      <c r="N13" s="11">
+        <f t="shared" si="1"/>
+        <v>19067.400000000001</v>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="6"/>
-        <v>-3.3842794759825212E-2</v>
-      </c>
-      <c r="P13" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q13" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R13" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+        <f t="shared" si="5"/>
+        <v>0.21057323093801439</v>
+      </c>
+      <c r="P13" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11">
+        <f t="shared" si="3"/>
+        <v>3316.6800000000003</v>
+      </c>
+      <c r="R13" s="12">
+        <f t="shared" si="4"/>
+        <v>0.21057323093801417</v>
       </c>
       <c r="S13" s="12">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <f ca="1">IF(W13=TRUE,IFERROR(N13/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <v>2.6103956377037982E-2</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="U13" s="6" t="s">
         <v>35</v>
@@ -2256,70 +2252,68 @@
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="7">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="H14" s="8">
-        <v>145.84</v>
+        <v>58.79</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="9">
-        <v>1</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="J14" s="9"/>
       <c r="K14" s="8">
-        <v>176.55</v>
-      </c>
-      <c r="L14" s="13">
-        <f>IF(I14="DKK",1,IFERROR(_xludf.XLOOKUP(I14,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="L14" s="13" t="str">
+        <f ca="1">IF(I14="DKK",1,IFERROR(_xludf.XLOOKUP(I14,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v/>
       </c>
       <c r="M14" s="11">
         <f t="shared" si="0"/>
-        <v>15750.720000000001</v>
-      </c>
-      <c r="N14" s="11">
-        <f t="shared" si="1"/>
-        <v>19067.400000000001</v>
+        <v>0</v>
+      </c>
+      <c r="N14" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="6"/>
-        <v>0.21057323093801439</v>
-      </c>
-      <c r="P14" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="11">
-        <f t="shared" si="3"/>
-        <v>3316.6800000000003</v>
-      </c>
-      <c r="R14" s="12">
-        <f t="shared" si="4"/>
-        <v>0.21057323093801417</v>
+        <f t="shared" si="5"/>
+        <v>-1.3437659465895591E-2</v>
+      </c>
+      <c r="P14" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q14" s="11" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R14" s="12" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="S14" s="12">
-        <f t="shared" ca="1" si="5"/>
-        <v>2.6103956377037982E-2</v>
+        <f ca="1">IF(W14=TRUE,IFERROR(N14/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <v>0</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="U14" s="6" t="s">
         <v>35</v>
@@ -2337,38 +2331,40 @@
         <v>37</v>
       </c>
       <c r="Z14" s="6"/>
-      <c r="AA14" s="14"/>
+      <c r="AA14" s="14" t="s">
+        <v>96</v>
+      </c>
       <c r="AB14" s="14"/>
     </row>
     <row r="15" spans="1:28">
       <c r="A15" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>93</v>
-      </c>
       <c r="C15" s="14" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="7">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="H15" s="8">
-        <v>58.79</v>
+        <v>44.308</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="J15" s="9"/>
       <c r="K15" s="8">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="L15" s="13" t="str">
         <f ca="1">IF(I15="DKK",1,IFERROR(_xludf.XLOOKUP(I15,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2383,8 +2379,8 @@
         <v/>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.3437659465895591E-2</v>
+        <f t="shared" si="5"/>
+        <v>8.3325810237429021E-2</v>
       </c>
       <c r="P15" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2399,11 +2395,11 @@
         <v/>
       </c>
       <c r="S15" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W15=TRUE,IFERROR(N15/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="U15" s="6" t="s">
         <v>35</v>
@@ -2421,75 +2417,52 @@
         <v>37</v>
       </c>
       <c r="Z15" s="6"/>
-      <c r="AA15" s="14" t="s">
-        <v>97</v>
-      </c>
+      <c r="AA15" s="14"/>
       <c r="AB15" s="14"/>
     </row>
     <row r="16" spans="1:28">
       <c r="A16" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>99</v>
+        <v>208</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>100</v>
+        <v>209</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="7">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="H16" s="8">
-        <v>44.308</v>
+        <v>78.83</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="8">
-        <v>48</v>
-      </c>
-      <c r="L16" s="13" t="str">
-        <f ca="1">IF(I16="DKK",1,IFERROR(_xludf.XLOOKUP(I16,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
-      </c>
-      <c r="M16" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
       <c r="O16" s="12">
-        <f t="shared" si="6"/>
-        <v>8.3325810237429021E-2</v>
-      </c>
-      <c r="P16" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q16" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R16" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S16" s="12">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>2.1565393885576434E-3</v>
+      </c>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
       <c r="T16" s="6" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="U16" s="6" t="s">
         <v>35</v>
@@ -2512,47 +2485,68 @@
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>210</v>
-      </c>
       <c r="D17" s="6" t="s">
-        <v>211</v>
+        <v>102</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>212</v>
+        <v>102</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="7">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H17" s="8">
-        <v>78.83</v>
+        <v>28.96</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="8">
-        <v>79</v>
-      </c>
-      <c r="L17" s="13"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="L17" s="13" t="str">
+        <f ca="1">IF(I17="DKK",1,IFERROR(_xludf.XLOOKUP(I17,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v/>
+      </c>
+      <c r="M17" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="O17" s="12">
-        <f t="shared" si="6"/>
-        <v>2.1565393885576434E-3</v>
-      </c>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
+        <f t="shared" si="5"/>
+        <v>-0.20580110497237569</v>
+      </c>
+      <c r="P17" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q17" s="11" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R17" s="12" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="S17" s="12">
+        <f ca="1">IF(W17=TRUE,IFERROR(N17/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <v>0</v>
+      </c>
       <c r="T17" s="6" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="U17" s="6" t="s">
         <v>35</v>
@@ -2575,33 +2569,33 @@
     </row>
     <row r="18" spans="1:28">
       <c r="A18" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>102</v>
-      </c>
       <c r="D18" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="7">
-        <v>52</v>
+        <v>185</v>
       </c>
       <c r="H18" s="8">
-        <v>28.96</v>
+        <v>10.622</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="8">
-        <v>23</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="L18" s="13" t="str">
         <f ca="1">IF(I18="DKK",1,IFERROR(_xludf.XLOOKUP(I18,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2616,8 +2610,8 @@
         <v/>
       </c>
       <c r="O18" s="12">
-        <f t="shared" si="6"/>
-        <v>-0.20580110497237569</v>
+        <f t="shared" si="5"/>
+        <v>-0.12445867068348704</v>
       </c>
       <c r="P18" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2632,11 +2626,11 @@
         <v/>
       </c>
       <c r="S18" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W18=TRUE,IFERROR(N18/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U18" s="6" t="s">
         <v>35</v>
@@ -2659,33 +2653,33 @@
     </row>
     <row r="19" spans="1:28">
       <c r="A19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>105</v>
-      </c>
       <c r="D19" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7">
-        <v>185</v>
+        <v>363</v>
       </c>
       <c r="H19" s="8">
-        <v>10.622</v>
+        <v>9</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="8">
-        <v>9.3000000000000007</v>
+        <v>17</v>
       </c>
       <c r="L19" s="13" t="str">
         <f ca="1">IF(I19="DKK",1,IFERROR(_xludf.XLOOKUP(I19,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2700,8 +2694,8 @@
         <v/>
       </c>
       <c r="O19" s="12">
-        <f t="shared" si="6"/>
-        <v>-0.12445867068348704</v>
+        <f t="shared" si="5"/>
+        <v>0.88888888888888884</v>
       </c>
       <c r="P19" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2716,11 +2710,11 @@
         <v/>
       </c>
       <c r="S19" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W19=TRUE,IFERROR(N19/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="U19" s="6" t="s">
         <v>35</v>
@@ -2743,33 +2737,33 @@
     </row>
     <row r="20" spans="1:28">
       <c r="A20" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>108</v>
-      </c>
       <c r="D20" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="7">
-        <v>363</v>
+        <v>19</v>
       </c>
       <c r="H20" s="8">
-        <v>9</v>
+        <v>114.15900000000001</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="8">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="L20" s="13" t="str">
         <f ca="1">IF(I20="DKK",1,IFERROR(_xludf.XLOOKUP(I20,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2784,8 +2778,8 @@
         <v/>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="6"/>
-        <v>0.88888888888888884</v>
+        <f t="shared" si="5"/>
+        <v>-8.0230205240059971E-2</v>
       </c>
       <c r="P20" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2800,7 +2794,7 @@
         <v/>
       </c>
       <c r="S20" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -2827,33 +2821,33 @@
     </row>
     <row r="21" spans="1:28">
       <c r="A21" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>111</v>
-      </c>
       <c r="D21" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="7">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="H21" s="8">
-        <v>114.15900000000001</v>
+        <v>8.6419999999999995</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="8">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="L21" s="13" t="str">
         <f ca="1">IF(I21="DKK",1,IFERROR(_xludf.XLOOKUP(I21,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2868,8 +2862,8 @@
         <v/>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="6"/>
-        <v>-8.0230205240059971E-2</v>
+        <f t="shared" si="5"/>
+        <v>-7.4288359176116536E-2</v>
       </c>
       <c r="P21" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2884,11 +2878,11 @@
         <v/>
       </c>
       <c r="S21" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W21=TRUE,IFERROR(N21/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="U21" s="6" t="s">
         <v>35</v>
@@ -2911,33 +2905,33 @@
     </row>
     <row r="22" spans="1:28">
       <c r="A22" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>114</v>
-      </c>
       <c r="D22" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="H22" s="8">
-        <v>8.6419999999999995</v>
+        <v>56.9</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="8">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="L22" s="13" t="str">
         <f ca="1">IF(I22="DKK",1,IFERROR(_xludf.XLOOKUP(I22,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2952,8 +2946,8 @@
         <v/>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.4288359176116536E-2</v>
+        <f t="shared" si="5"/>
+        <v>-1.5817223198594021E-2</v>
       </c>
       <c r="P22" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2968,11 +2962,11 @@
         <v/>
       </c>
       <c r="S22" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W22=TRUE,IFERROR(N22/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="U22" s="6" t="s">
         <v>35</v>
@@ -2995,33 +2989,33 @@
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>118</v>
-      </c>
       <c r="D23" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H23" s="8">
-        <v>56.9</v>
+        <v>27.972000000000001</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="8">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="L23" s="13" t="str">
         <f ca="1">IF(I23="DKK",1,IFERROR(_xludf.XLOOKUP(I23,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3036,8 +3030,8 @@
         <v/>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="6"/>
-        <v>-1.5817223198594021E-2</v>
+        <f t="shared" si="5"/>
+        <v>-7.049907049907056E-2</v>
       </c>
       <c r="P23" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3052,11 +3046,11 @@
         <v/>
       </c>
       <c r="S23" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W23=TRUE,IFERROR(N23/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="U23" s="6" t="s">
         <v>35</v>
@@ -3079,33 +3073,33 @@
     </row>
     <row r="24" spans="1:28">
       <c r="A24" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>122</v>
-      </c>
       <c r="D24" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="7">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c r="H24" s="8">
-        <v>27.972000000000001</v>
+        <v>16.594000000000001</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="8">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="L24" s="13" t="str">
         <f ca="1">IF(I24="DKK",1,IFERROR(_xludf.XLOOKUP(I24,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3120,8 +3114,8 @@
         <v/>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.049907049907056E-2</v>
+        <f t="shared" si="5"/>
+        <v>-0.27684705315174163</v>
       </c>
       <c r="P24" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3136,11 +3130,11 @@
         <v/>
       </c>
       <c r="S24" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W24=TRUE,IFERROR(N24/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="U24" s="6" t="s">
         <v>35</v>
@@ -3163,33 +3157,33 @@
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>125</v>
-      </c>
       <c r="D25" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7">
-        <v>161</v>
+        <v>46</v>
       </c>
       <c r="H25" s="8">
-        <v>16.594000000000001</v>
+        <v>55.45</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="8">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="L25" s="13" t="str">
         <f ca="1">IF(I25="DKK",1,IFERROR(_xludf.XLOOKUP(I25,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3204,8 +3198,8 @@
         <v/>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="6"/>
-        <v>-0.27684705315174163</v>
+        <f t="shared" si="5"/>
+        <v>-2.6149684400360695E-2</v>
       </c>
       <c r="P25" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3220,11 +3214,11 @@
         <v/>
       </c>
       <c r="S25" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W25=TRUE,IFERROR(N25/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="U25" s="6" t="s">
         <v>35</v>
@@ -3247,33 +3241,33 @@
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>128</v>
-      </c>
       <c r="D26" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H26" s="8">
-        <v>55.45</v>
+        <v>95.08</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="8">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L26" s="13" t="str">
         <f ca="1">IF(I26="DKK",1,IFERROR(_xludf.XLOOKUP(I26,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3288,8 +3282,8 @@
         <v/>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.6149684400360695E-2</v>
+        <f t="shared" si="5"/>
+        <v>-0.2111905763567522</v>
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3304,11 +3298,11 @@
         <v/>
       </c>
       <c r="S26" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W26=TRUE,IFERROR(N26/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="U26" s="6" t="s">
         <v>35</v>
@@ -3331,33 +3325,33 @@
     </row>
     <row r="27" spans="1:28">
       <c r="A27" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>131</v>
-      </c>
       <c r="D27" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H27" s="8">
-        <v>95.08</v>
+        <v>77.56</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="8">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L27" s="13" t="str">
         <f ca="1">IF(I27="DKK",1,IFERROR(_xludf.XLOOKUP(I27,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3372,8 +3366,8 @@
         <v/>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="6"/>
-        <v>-0.2111905763567522</v>
+        <f t="shared" si="5"/>
+        <v>5.6730273336771386E-3</v>
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3388,11 +3382,11 @@
         <v/>
       </c>
       <c r="S27" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W27=TRUE,IFERROR(N27/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="U27" s="6" t="s">
         <v>35</v>
@@ -3415,33 +3409,33 @@
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>135</v>
-      </c>
       <c r="D28" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H28" s="8">
-        <v>77.56</v>
+        <v>159</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="8">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="L28" s="13" t="str">
         <f ca="1">IF(I28="DKK",1,IFERROR(_xludf.XLOOKUP(I28,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3456,8 +3450,8 @@
         <v/>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="6"/>
-        <v>5.6730273336771386E-3</v>
+        <f t="shared" si="5"/>
+        <v>5.6603773584905648E-2</v>
       </c>
       <c r="P28" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3472,14 +3466,14 @@
         <v/>
       </c>
       <c r="S28" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W28=TRUE,IFERROR(N28/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="U28" s="6" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="V28" s="10" t="b">
         <v>1</v>
@@ -3499,74 +3493,76 @@
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>138</v>
-      </c>
       <c r="D29" s="6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7">
-        <v>18</v>
+        <v>260</v>
       </c>
       <c r="H29" s="8">
-        <v>159</v>
+        <v>606</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J29" s="9"/>
+        <v>42</v>
+      </c>
+      <c r="J29" s="9">
+        <v>1</v>
+      </c>
       <c r="K29" s="8">
-        <v>168</v>
-      </c>
-      <c r="L29" s="13" t="str">
-        <f ca="1">IF(I29="DKK",1,IFERROR(_xludf.XLOOKUP(I29,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
+        <v>1662</v>
+      </c>
+      <c r="L29" s="13">
+        <f>IF(I29="DKK",1,IFERROR(_xludf.XLOOKUP(I29,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
       </c>
       <c r="M29" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>157560</v>
+      </c>
+      <c r="N29" s="11">
+        <f t="shared" si="1"/>
+        <v>432120</v>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="6"/>
-        <v>5.6603773584905648E-2</v>
-      </c>
-      <c r="P29" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q29" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R29" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+        <f t="shared" si="5"/>
+        <v>1.7425742574257428</v>
+      </c>
+      <c r="P29" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="11">
+        <f t="shared" si="3"/>
+        <v>274560</v>
+      </c>
+      <c r="R29" s="12">
+        <f t="shared" si="4"/>
+        <v>1.7425742574257428</v>
       </c>
       <c r="S29" s="12">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <f ca="1">IF(W29=TRUE,IFERROR(N29/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <v>0.5915878216036613</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="U29" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="V29" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W29" s="10" t="b">
         <v>1</v>
@@ -3581,96 +3577,10 @@
       <c r="AA29" s="14"/>
       <c r="AB29" s="14"/>
     </row>
-    <row r="30" spans="1:28">
-      <c r="A30" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="7">
-        <v>260</v>
-      </c>
-      <c r="H30" s="8">
-        <v>606</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J30" s="9">
-        <v>1</v>
-      </c>
-      <c r="K30" s="8">
-        <v>1662</v>
-      </c>
-      <c r="L30" s="13">
-        <f>IF(I30="DKK",1,IFERROR(_xludf.XLOOKUP(I30,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
-      </c>
-      <c r="M30" s="11">
-        <f t="shared" si="0"/>
-        <v>157560</v>
-      </c>
-      <c r="N30" s="11">
-        <f t="shared" si="1"/>
-        <v>432120</v>
-      </c>
-      <c r="O30" s="12">
-        <f t="shared" si="6"/>
-        <v>1.7425742574257428</v>
-      </c>
-      <c r="P30" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="11">
-        <f t="shared" si="3"/>
-        <v>274560</v>
-      </c>
-      <c r="R30" s="12">
-        <f t="shared" si="4"/>
-        <v>1.7425742574257428</v>
-      </c>
-      <c r="S30" s="12">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.5915878216036613</v>
-      </c>
-      <c r="T30" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="U30" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="V30" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="W30" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="X30" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y30" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z30" s="6"/>
-      <c r="AA30" s="14"/>
-      <c r="AB30" s="14"/>
-    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="G2:S30">
+  <conditionalFormatting sqref="G2:S29">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -3700,16 +3610,16 @@
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>27</v>
@@ -3720,7 +3630,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
@@ -3734,13 +3644,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D3" s="1" t="b">
         <v>1</v>
@@ -3751,22 +3661,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" t="s">
         <v>150</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>151</v>
-      </c>
-      <c r="D4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
-        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -3790,150 +3700,150 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B2" t="s">
         <v>157</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>158</v>
-      </c>
-      <c r="D2" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B3" s="5">
         <v>0.02</v>
       </c>
       <c r="C3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" t="s">
         <v>161</v>
-      </c>
-      <c r="D3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B4" s="5">
         <v>0.14000000000000001</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B5" s="5">
         <v>0.2</v>
       </c>
       <c r="C5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B6" s="5">
         <v>0.25</v>
       </c>
       <c r="C6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B7" s="5">
         <v>0.25</v>
       </c>
       <c r="C7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B8" s="5">
         <v>0.2</v>
       </c>
       <c r="C8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B9" s="5">
         <v>0.1</v>
       </c>
       <c r="C9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10" t="s">
         <v>171</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
         <v>172</v>
-      </c>
-      <c r="D10" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" t="s">
         <v>175</v>
-      </c>
-      <c r="D11" t="s">
-        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -3971,19 +3881,19 @@
         <v>11</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3994,16 +3904,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
         <v>182</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4012,13 +3922,13 @@
       </c>
       <c r="B3" s="3"/>
       <c r="D3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
         <v>184</v>
-      </c>
-      <c r="F3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4027,13 +3937,13 @@
       </c>
       <c r="B4" s="3"/>
       <c r="D4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
         <v>184</v>
-      </c>
-      <c r="F4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4042,73 +3952,73 @@
       </c>
       <c r="B5" s="3"/>
       <c r="D5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
         <v>184</v>
-      </c>
-      <c r="F5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B6" s="3"/>
       <c r="D6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
         <v>184</v>
-      </c>
-      <c r="F6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B7" s="3"/>
       <c r="D7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
         <v>184</v>
-      </c>
-      <c r="F7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B8" s="3"/>
       <c r="D8" t="s">
+        <v>183</v>
+      </c>
+      <c r="F8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
         <v>184</v>
-      </c>
-      <c r="F8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B9" s="3"/>
       <c r="D9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
         <v>184</v>
-      </c>
-      <c r="F9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -4145,16 +4055,16 @@
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4165,16 +4075,16 @@
         <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4185,16 +4095,16 @@
         <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D3" t="s">
         <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4205,16 +4115,16 @@
         <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D4" t="s">
         <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4225,16 +4135,16 @@
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D5" t="s">
         <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4248,10 +4158,10 @@
         <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4262,16 +4172,16 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D7" t="s">
         <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4285,10 +4195,10 @@
         <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4302,10 +4212,10 @@
         <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4316,16 +4226,16 @@
         <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D10" t="s">
         <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4336,16 +4246,16 @@
         <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D11" t="s">
         <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4356,314 +4266,314 @@
         <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D12" t="s">
         <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" t="s">
         <v>85</v>
       </c>
-      <c r="B13" t="s">
-        <v>86</v>
-      </c>
       <c r="C13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
         <v>89</v>
       </c>
-      <c r="B14" t="s">
-        <v>90</v>
-      </c>
       <c r="C14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D14" t="s">
         <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D15" t="s">
         <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
         <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
         <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
         <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
         <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
         <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F27" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D28" t="s">
         <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F28" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D29" t="s">
         <v>42</v>
       </c>
       <c r="E29" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -4708,16 +4618,16 @@
         <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>27</v>
@@ -4725,7 +4635,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="F2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -4762,19 +4672,19 @@
         <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="F1" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:7">

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD5C251-1E50-4022-B15A-3C17CD01AA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CF7B74-21B8-4229-91E9-40A82FA9C7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -671,7 +671,7 @@
     <t>IS3Q:XETR</t>
   </si>
   <si>
-    <t>IS3Q:DE</t>
+    <t>IS3Q.DE</t>
   </si>
 </sst>
 </file>
@@ -1289,7 +1289,7 @@
         <v/>
       </c>
       <c r="S2" s="12">
-        <f ca="1">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ref="S2:S15" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1359,7 +1359,7 @@
         <v>31875</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" ref="O3:O29" si="5">IFERROR(K3/H3-1,"")</f>
+        <f t="shared" ref="O3:O29" si="6">IFERROR(K3/H3-1,"")</f>
         <v>0.46054802052785915</v>
       </c>
       <c r="P3" s="12">
@@ -1375,7 +1375,7 @@
         <v>0.46054802052785915</v>
       </c>
       <c r="S3" s="12">
-        <f ca="1">IF(W3=TRUE,IFERROR(N3/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>4.3638021414460576E-2</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -1443,7 +1443,7 @@
         <v/>
       </c>
       <c r="O4" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.38822722512118468</v>
       </c>
       <c r="P4" s="12" t="str">
@@ -1459,7 +1459,7 @@
         <v/>
       </c>
       <c r="S4" s="12">
-        <f ca="1">IF(W4=TRUE,IFERROR(N4/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -1529,7 +1529,7 @@
         <v>57742.2</v>
       </c>
       <c r="O5" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.88549160671462812</v>
       </c>
       <c r="P5" s="12">
@@ -1545,7 +1545,7 @@
         <v>0.88549160671462812</v>
       </c>
       <c r="S5" s="12">
-        <f ca="1">IF(W5=TRUE,IFERROR(N5/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>7.9051148552723619E-2</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -1613,7 +1613,7 @@
         <v/>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.5263417035942806E-2</v>
       </c>
       <c r="P6" s="12" t="str">
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="S6" s="12">
-        <f ca="1">IF(W6=TRUE,IFERROR(N6/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -1697,7 +1697,7 @@
         <v/>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.5135023706452326E-2</v>
       </c>
       <c r="P7" s="12" t="str">
@@ -1713,7 +1713,7 @@
         <v/>
       </c>
       <c r="S7" s="12">
-        <f ca="1">IF(W7=TRUE,IFERROR(N7/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -1783,7 +1783,7 @@
         <v>57330</v>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.2431473082232301</v>
       </c>
       <c r="P8" s="12">
@@ -1799,7 +1799,7 @@
         <v>1.2431473082232301</v>
       </c>
       <c r="S8" s="12">
-        <f ca="1">IF(W8=TRUE,IFERROR(N8/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>7.8486831927561562E-2</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -1869,7 +1869,7 @@
         <v>100128</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.32731376975169302</v>
       </c>
       <c r="P9" s="12">
@@ -1885,7 +1885,7 @@
         <v>-0.32731376975169302</v>
       </c>
       <c r="S9" s="12">
-        <f ca="1">IF(W9=TRUE,IFERROR(N9/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0.13707883319802694</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -1955,7 +1955,7 @@
         <v>32178.399999999998</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.34070074887984658</v>
       </c>
       <c r="P10" s="12">
@@ -1971,7 +1971,7 @@
         <v>0.34070074887984658</v>
       </c>
       <c r="S10" s="12">
-        <f ca="1">IF(W10=TRUE,IFERROR(N10/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>4.4053386926527945E-2</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -2039,7 +2039,7 @@
         <v/>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.10727323785453535</v>
       </c>
       <c r="P11" s="12" t="str">
@@ -2055,7 +2055,7 @@
         <v/>
       </c>
       <c r="S11" s="12">
-        <f ca="1">IF(W11=TRUE,IFERROR(N11/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.1743119266054496E-3</v>
       </c>
       <c r="P12" s="12" t="str">
@@ -2139,7 +2139,7 @@
         <v/>
       </c>
       <c r="S12" s="12">
-        <f ca="1">IF(W12=TRUE,IFERROR(N12/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -2209,7 +2209,7 @@
         <v>19067.400000000001</v>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.21057323093801439</v>
       </c>
       <c r="P13" s="12">
@@ -2225,7 +2225,7 @@
         <v>0.21057323093801417</v>
       </c>
       <c r="S13" s="12">
-        <f ca="1">IF(W13=TRUE,IFERROR(N13/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>2.6103956377037982E-2</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -2293,7 +2293,7 @@
         <v/>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.3437659465895591E-2</v>
       </c>
       <c r="P14" s="12" t="str">
@@ -2309,7 +2309,7 @@
         <v/>
       </c>
       <c r="S14" s="12">
-        <f ca="1">IF(W14=TRUE,IFERROR(N14/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -2379,7 +2379,7 @@
         <v/>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.3325810237429021E-2</v>
       </c>
       <c r="P15" s="12" t="str">
@@ -2395,7 +2395,7 @@
         <v/>
       </c>
       <c r="S15" s="12">
-        <f ca="1">IF(W15=TRUE,IFERROR(N15/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T15" s="6" t="s">
@@ -2454,7 +2454,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.1565393885576434E-3</v>
       </c>
       <c r="P16" s="12"/>
@@ -2526,7 +2526,7 @@
         <v/>
       </c>
       <c r="O17" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.20580110497237569</v>
       </c>
       <c r="P17" s="12" t="str">
@@ -2542,7 +2542,7 @@
         <v/>
       </c>
       <c r="S17" s="12">
-        <f ca="1">IF(W17=TRUE,IFERROR(N17/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ref="S17:S29" ca="1" si="7">IF(W17=TRUE,IFERROR(N17/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -2610,7 +2610,7 @@
         <v/>
       </c>
       <c r="O18" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.12445867068348704</v>
       </c>
       <c r="P18" s="12" t="str">
@@ -2626,7 +2626,7 @@
         <v/>
       </c>
       <c r="S18" s="12">
-        <f ca="1">IF(W18=TRUE,IFERROR(N18/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -2694,7 +2694,7 @@
         <v/>
       </c>
       <c r="O19" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="P19" s="12" t="str">
@@ -2710,7 +2710,7 @@
         <v/>
       </c>
       <c r="S19" s="12">
-        <f ca="1">IF(W19=TRUE,IFERROR(N19/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T19" s="6" t="s">
@@ -2778,7 +2778,7 @@
         <v/>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-8.0230205240059971E-2</v>
       </c>
       <c r="P20" s="12" t="str">
@@ -2794,7 +2794,7 @@
         <v/>
       </c>
       <c r="S20" s="12">
-        <f ca="1">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -2862,7 +2862,7 @@
         <v/>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-7.4288359176116536E-2</v>
       </c>
       <c r="P21" s="12" t="str">
@@ -2878,7 +2878,7 @@
         <v/>
       </c>
       <c r="S21" s="12">
-        <f ca="1">IF(W21=TRUE,IFERROR(N21/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -2946,7 +2946,7 @@
         <v/>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.5817223198594021E-2</v>
       </c>
       <c r="P22" s="12" t="str">
@@ -2962,7 +2962,7 @@
         <v/>
       </c>
       <c r="S22" s="12">
-        <f ca="1">IF(W22=TRUE,IFERROR(N22/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -3030,7 +3030,7 @@
         <v/>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-7.049907049907056E-2</v>
       </c>
       <c r="P23" s="12" t="str">
@@ -3046,7 +3046,7 @@
         <v/>
       </c>
       <c r="S23" s="12">
-        <f ca="1">IF(W23=TRUE,IFERROR(N23/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -3114,7 +3114,7 @@
         <v/>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.27684705315174163</v>
       </c>
       <c r="P24" s="12" t="str">
@@ -3130,7 +3130,7 @@
         <v/>
       </c>
       <c r="S24" s="12">
-        <f ca="1">IF(W24=TRUE,IFERROR(N24/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -3198,7 +3198,7 @@
         <v/>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-2.6149684400360695E-2</v>
       </c>
       <c r="P25" s="12" t="str">
@@ -3214,7 +3214,7 @@
         <v/>
       </c>
       <c r="S25" s="12">
-        <f ca="1">IF(W25=TRUE,IFERROR(N25/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -3282,7 +3282,7 @@
         <v/>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.2111905763567522</v>
       </c>
       <c r="P26" s="12" t="str">
@@ -3298,7 +3298,7 @@
         <v/>
       </c>
       <c r="S26" s="12">
-        <f ca="1">IF(W26=TRUE,IFERROR(N26/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -3366,7 +3366,7 @@
         <v/>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.6730273336771386E-3</v>
       </c>
       <c r="P27" s="12" t="str">
@@ -3382,7 +3382,7 @@
         <v/>
       </c>
       <c r="S27" s="12">
-        <f ca="1">IF(W27=TRUE,IFERROR(N27/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -3450,7 +3450,7 @@
         <v/>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.6603773584905648E-2</v>
       </c>
       <c r="P28" s="12" t="str">
@@ -3466,7 +3466,7 @@
         <v/>
       </c>
       <c r="S28" s="12">
-        <f ca="1">IF(W28=TRUE,IFERROR(N28/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -3536,7 +3536,7 @@
         <v>432120</v>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.7425742574257428</v>
       </c>
       <c r="P29" s="12">
@@ -3552,7 +3552,7 @@
         <v>1.7425742574257428</v>
       </c>
       <c r="S29" s="12">
-        <f ca="1">IF(W29=TRUE,IFERROR(N29/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0.5915878216036613</v>
       </c>
       <c r="T29" s="6" t="s">

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CF7B74-21B8-4229-91E9-40A82FA9C7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E68C5E-8A1A-4F7F-8E1B-CD7F33A793CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1672,10 +1672,10 @@
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7" s="8">
-        <v>388.08</v>
+        <v>394.77</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>48</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="6"/>
-        <v>9.5135023706452326E-2</v>
+        <v>7.6576234262988541E-2</v>
       </c>
       <c r="P7" s="12" t="str">
         <f t="shared" ca="1" si="2"/>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E68C5E-8A1A-4F7F-8E1B-CD7F33A793CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCBF1A9-5273-42B8-BA92-3AD4BAA5376F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2268,10 +2268,10 @@
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="7">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="H14" s="8">
-        <v>58.79</v>
+        <v>59.2</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>57</v>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="O14" s="12">
         <f t="shared" si="6"/>
-        <v>-1.3437659465895591E-2</v>
+        <v>-2.0270270270270285E-2</v>
       </c>
       <c r="P14" s="12" t="str">
         <f t="shared" ca="1" si="2"/>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCBF1A9-5273-42B8-BA92-3AD4BAA5376F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F110AF1-57B6-466D-94FB-B6048DABFA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="214">
   <si>
     <t>Asset_ID</t>
   </si>
@@ -638,9 +638,6 @@
     <t>XLON</t>
   </si>
   <si>
-    <t>VERIFY</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -672,6 +669,18 @@
   </si>
   <si>
     <t>IS3Q.DE</t>
+  </si>
+  <si>
+    <t>A029</t>
+  </si>
+  <si>
+    <t>ServiceNow Inc</t>
+  </si>
+  <si>
+    <t>4S0.DE</t>
+  </si>
+  <si>
+    <t>4S0:XETR</t>
   </si>
 </sst>
 </file>
@@ -839,7 +848,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PortfolioTable" displayName="PortfolioTable" ref="A1:AB30">
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Asset_ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Asset_Type"/>
@@ -916,7 +925,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TickerMapTable" displayName="TickerMapTable" ref="A1:F29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TickerMapTable" displayName="TickerMapTable" ref="A1:F31">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Ticker"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Yahoo_Ticker"/>
@@ -1111,7 +1120,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB29"/>
+  <sheetPr codeName="Sheet1">
+    <tabColor theme="3" tint="0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -1265,7 +1277,7 @@
         <v/>
       </c>
       <c r="M2" s="11">
-        <f t="shared" ref="M2:M29" si="0">IFERROR(G2*H2*J2,"")</f>
+        <f t="shared" ref="M2:M30" si="0">IFERROR(G2*H2*J2,"")</f>
         <v>0</v>
       </c>
       <c r="N2" s="11" t="str">
@@ -1277,19 +1289,19 @@
         <v>0.13468237048427878</v>
       </c>
       <c r="P2" s="12" t="str">
-        <f t="shared" ref="P2:P29" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
+        <f t="shared" ref="P2:P30" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
         <v/>
       </c>
       <c r="Q2" s="11" t="str">
-        <f t="shared" ref="Q2:Q29" ca="1" si="3">IFERROR(N2-M2,"")</f>
+        <f t="shared" ref="Q2:Q30" ca="1" si="3">IFERROR(N2-M2,"")</f>
         <v/>
       </c>
       <c r="R2" s="12" t="str">
-        <f t="shared" ref="R2:R29" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
+        <f t="shared" ref="R2:R30" ca="1" si="4">IFERROR(N2/M2-1,"")</f>
         <v/>
       </c>
       <c r="S2" s="12">
-        <f t="shared" ref="S2:S15" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
+        <f t="shared" ref="S2:S16" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1359,7 +1371,7 @@
         <v>31875</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" ref="O3:O29" si="6">IFERROR(K3/H3-1,"")</f>
+        <f t="shared" ref="O3:O30" si="6">IFERROR(K3/H3-1,"")</f>
         <v>0.46054802052785915</v>
       </c>
       <c r="P3" s="12">
@@ -1588,7 +1600,7 @@
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="7">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="H6" s="8">
         <v>40.619999999999997</v>
@@ -2004,62 +2016,53 @@
         <v>29</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H11" s="8">
-        <v>142.44</v>
+        <v>110.34</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="8">
-        <v>157.72</v>
-      </c>
-      <c r="L11" s="13" t="str">
-        <f ca="1">IF(I11="DKK",1,IFERROR(_xludf.XLOOKUP(I11,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
-      </c>
-      <c r="M11" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
+        <v>110.8</v>
+      </c>
+      <c r="L11" s="13"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
       <c r="O11" s="12">
-        <f t="shared" si="6"/>
-        <v>0.10727323785453535</v>
+        <f t="shared" ref="O11" si="7">IFERROR(K11/H11-1,"")</f>
+        <v>4.1689323907920794E-3</v>
       </c>
       <c r="P11" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q11" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
+        <f t="shared" ref="P11" si="8">IFERROR(L11/J11-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q11" s="11">
+        <f t="shared" ref="Q11" si="9">IFERROR(N11-M11,"")</f>
+        <v>0</v>
       </c>
       <c r="R11" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ref="R11" si="10">IFERROR(N11/M11-1,"")</f>
         <v/>
       </c>
       <c r="S11" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ref="S11" ca="1" si="11">IF(W11=TRUE,IFERROR(N11/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="U11" s="6" t="s">
         <v>35</v>
@@ -2088,27 +2091,27 @@
         <v>29</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="7">
         <v>14</v>
       </c>
       <c r="H12" s="8">
-        <v>414.2</v>
+        <v>142.44</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="8">
-        <v>418</v>
+        <v>157.72</v>
       </c>
       <c r="L12" s="13" t="str">
         <f ca="1">IF(I12="DKK",1,IFERROR(_xludf.XLOOKUP(I12,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2124,7 +2127,7 @@
       </c>
       <c r="O12" s="12">
         <f t="shared" si="6"/>
-        <v>9.1743119266054496E-3</v>
+        <v>0.10727323785453535</v>
       </c>
       <c r="P12" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2143,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="U12" s="6" t="s">
         <v>35</v>
@@ -2172,64 +2175,62 @@
         <v>29</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="7">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="H13" s="8">
-        <v>145.84</v>
+        <v>414.2</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="9">
-        <v>1</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="J13" s="9"/>
       <c r="K13" s="8">
-        <v>176.55</v>
-      </c>
-      <c r="L13" s="13">
-        <f>IF(I13="DKK",1,IFERROR(_xludf.XLOOKUP(I13,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
+        <v>418</v>
+      </c>
+      <c r="L13" s="13" t="str">
+        <f ca="1">IF(I13="DKK",1,IFERROR(_xludf.XLOOKUP(I13,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v/>
       </c>
       <c r="M13" s="11">
         <f t="shared" si="0"/>
-        <v>15750.720000000001</v>
-      </c>
-      <c r="N13" s="11">
-        <f t="shared" si="1"/>
-        <v>19067.400000000001</v>
+        <v>0</v>
+      </c>
+      <c r="N13" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="O13" s="12">
         <f t="shared" si="6"/>
-        <v>0.21057323093801439</v>
-      </c>
-      <c r="P13" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="11">
-        <f t="shared" si="3"/>
-        <v>3316.6800000000003</v>
-      </c>
-      <c r="R13" s="12">
-        <f t="shared" si="4"/>
-        <v>0.21057323093801417</v>
+        <v>9.1743119266054496E-3</v>
+      </c>
+      <c r="P13" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q13" s="11" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R13" s="12" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="S13" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.6103956377037982E-2</v>
+        <v>0</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="U13" s="6" t="s">
         <v>35</v>
@@ -2255,65 +2256,67 @@
         <v>86</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="7">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="H14" s="8">
-        <v>59.2</v>
+        <v>145.84</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="J14" s="9"/>
+        <v>42</v>
+      </c>
+      <c r="J14" s="9">
+        <v>1</v>
+      </c>
       <c r="K14" s="8">
-        <v>58</v>
-      </c>
-      <c r="L14" s="13" t="str">
-        <f ca="1">IF(I14="DKK",1,IFERROR(_xludf.XLOOKUP(I14,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
+        <v>176.55</v>
+      </c>
+      <c r="L14" s="13">
+        <f>IF(I14="DKK",1,IFERROR(_xludf.XLOOKUP(I14,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
       </c>
       <c r="M14" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
+        <f>IFERROR(G14*H14*J14,"")</f>
+        <v>15750.720000000001</v>
+      </c>
+      <c r="N14" s="11">
+        <f t="shared" si="1"/>
+        <v>19067.400000000001</v>
       </c>
       <c r="O14" s="12">
         <f t="shared" si="6"/>
-        <v>-2.0270270270270285E-2</v>
-      </c>
-      <c r="P14" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q14" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R14" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>0.21057323093801439</v>
+      </c>
+      <c r="P14" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="11">
+        <f t="shared" si="3"/>
+        <v>3316.6800000000003</v>
+      </c>
+      <c r="R14" s="12">
+        <f t="shared" si="4"/>
+        <v>0.21057323093801417</v>
       </c>
       <c r="S14" s="12">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>2.6103956377037982E-2</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="U14" s="6" t="s">
         <v>35</v>
@@ -2331,9 +2334,7 @@
         <v>37</v>
       </c>
       <c r="Z14" s="6"/>
-      <c r="AA14" s="14" t="s">
-        <v>96</v>
-      </c>
+      <c r="AA14" s="14"/>
       <c r="AB14" s="14"/>
     </row>
     <row r="15" spans="1:28">
@@ -2344,27 +2345,27 @@
         <v>92</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="7">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="H15" s="8">
-        <v>44.308</v>
+        <v>59.2</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J15" s="9"/>
       <c r="K15" s="8">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L15" s="13" t="str">
         <f ca="1">IF(I15="DKK",1,IFERROR(_xludf.XLOOKUP(I15,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2380,7 +2381,7 @@
       </c>
       <c r="O15" s="12">
         <f t="shared" si="6"/>
-        <v>8.3325810237429021E-2</v>
+        <v>-2.0270270270270285E-2</v>
       </c>
       <c r="P15" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2399,7 +2400,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="U15" s="6" t="s">
         <v>35</v>
@@ -2417,7 +2418,9 @@
         <v>37</v>
       </c>
       <c r="Z15" s="6"/>
-      <c r="AA15" s="14"/>
+      <c r="AA15" s="14" t="s">
+        <v>96</v>
+      </c>
       <c r="AB15" s="14"/>
     </row>
     <row r="16" spans="1:28">
@@ -2428,41 +2431,62 @@
         <v>92</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>208</v>
+        <v>98</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>209</v>
+        <v>99</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>210</v>
+        <v>99</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="7">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="H16" s="8">
-        <v>78.83</v>
+        <v>44.308</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="8">
-        <v>79</v>
-      </c>
-      <c r="L16" s="13"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
+        <v>48</v>
+      </c>
+      <c r="L16" s="13" t="str">
+        <f ca="1">IF(I16="DKK",1,IFERROR(_xludf.XLOOKUP(I16,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v/>
+      </c>
+      <c r="M16" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
       <c r="O16" s="12">
         <f t="shared" si="6"/>
-        <v>2.1565393885576434E-3</v>
-      </c>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
+        <v>8.3325810237429021E-2</v>
+      </c>
+      <c r="P16" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q16" s="11" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R16" s="12" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="S16" s="12">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
       <c r="T16" s="6" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="U16" s="6" t="s">
         <v>35</v>
@@ -2491,62 +2515,41 @@
         <v>92</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>102</v>
+        <v>209</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="7">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="H17" s="8">
-        <v>28.96</v>
+        <v>78.83</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="8">
-        <v>23</v>
-      </c>
-      <c r="L17" s="13" t="str">
-        <f ca="1">IF(I17="DKK",1,IFERROR(_xludf.XLOOKUP(I17,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
-      </c>
-      <c r="M17" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
       <c r="O17" s="12">
         <f t="shared" si="6"/>
-        <v>-0.20580110497237569</v>
-      </c>
-      <c r="P17" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q17" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R17" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S17" s="12">
-        <f t="shared" ref="S17:S29" ca="1" si="7">IF(W17=TRUE,IFERROR(N17/SUMIFS($N$2:$N$500,$W$2:$W$500,TRUE),0),0)</f>
-        <v>0</v>
-      </c>
+        <v>2.1565393885576434E-3</v>
+      </c>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
       <c r="T17" s="6" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="U17" s="6" t="s">
         <v>35</v>
@@ -2575,27 +2578,27 @@
         <v>92</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="7">
-        <v>185</v>
+        <v>52</v>
       </c>
       <c r="H18" s="8">
-        <v>10.622</v>
+        <v>28.96</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="8">
-        <v>9.3000000000000007</v>
+        <v>23</v>
       </c>
       <c r="L18" s="13" t="str">
         <f ca="1">IF(I18="DKK",1,IFERROR(_xludf.XLOOKUP(I18,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2611,7 +2614,7 @@
       </c>
       <c r="O18" s="12">
         <f t="shared" si="6"/>
-        <v>-0.12445867068348704</v>
+        <v>-0.20580110497237569</v>
       </c>
       <c r="P18" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2626,7 +2629,7 @@
         <v/>
       </c>
       <c r="S18" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ref="S18:S30" ca="1" si="12">IF(W18=TRUE,IFERROR(N18/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -2659,27 +2662,27 @@
         <v>92</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7">
-        <v>363</v>
+        <v>185</v>
       </c>
       <c r="H19" s="8">
-        <v>9</v>
+        <v>10.622</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="8">
-        <v>17</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="L19" s="13" t="str">
         <f ca="1">IF(I19="DKK",1,IFERROR(_xludf.XLOOKUP(I19,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2695,7 +2698,7 @@
       </c>
       <c r="O19" s="12">
         <f t="shared" si="6"/>
-        <v>0.88888888888888884</v>
+        <v>-0.12445867068348704</v>
       </c>
       <c r="P19" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2710,11 +2713,11 @@
         <v/>
       </c>
       <c r="S19" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="U19" s="6" t="s">
         <v>35</v>
@@ -2743,27 +2746,27 @@
         <v>92</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="7">
-        <v>19</v>
+        <v>363</v>
       </c>
       <c r="H20" s="8">
-        <v>114.15900000000001</v>
+        <v>9</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="8">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="L20" s="13" t="str">
         <f ca="1">IF(I20="DKK",1,IFERROR(_xludf.XLOOKUP(I20,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2779,7 +2782,7 @@
       </c>
       <c r="O20" s="12">
         <f t="shared" si="6"/>
-        <v>-8.0230205240059971E-2</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="P20" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2794,7 +2797,7 @@
         <v/>
       </c>
       <c r="S20" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -2827,27 +2830,27 @@
         <v>92</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="7">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="H21" s="8">
-        <v>8.6419999999999995</v>
+        <v>114.15900000000001</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="8">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="L21" s="13" t="str">
         <f ca="1">IF(I21="DKK",1,IFERROR(_xludf.XLOOKUP(I21,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2863,7 +2866,7 @@
       </c>
       <c r="O21" s="12">
         <f t="shared" si="6"/>
-        <v>-7.4288359176116536E-2</v>
+        <v>-8.0230205240059971E-2</v>
       </c>
       <c r="P21" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2878,11 +2881,11 @@
         <v/>
       </c>
       <c r="S21" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="U21" s="6" t="s">
         <v>35</v>
@@ -2911,27 +2914,27 @@
         <v>92</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="H22" s="8">
-        <v>56.9</v>
+        <v>8.6419999999999995</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="8">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="L22" s="13" t="str">
         <f ca="1">IF(I22="DKK",1,IFERROR(_xludf.XLOOKUP(I22,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -2947,7 +2950,7 @@
       </c>
       <c r="O22" s="12">
         <f t="shared" si="6"/>
-        <v>-1.5817223198594021E-2</v>
+        <v>-7.4288359176116536E-2</v>
       </c>
       <c r="P22" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2962,11 +2965,11 @@
         <v/>
       </c>
       <c r="S22" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="U22" s="6" t="s">
         <v>35</v>
@@ -2995,27 +2998,27 @@
         <v>92</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H23" s="8">
-        <v>27.972000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="8">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="L23" s="13" t="str">
         <f ca="1">IF(I23="DKK",1,IFERROR(_xludf.XLOOKUP(I23,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3031,7 +3034,7 @@
       </c>
       <c r="O23" s="12">
         <f t="shared" si="6"/>
-        <v>-7.049907049907056E-2</v>
+        <v>-1.5817223198594021E-2</v>
       </c>
       <c r="P23" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3046,11 +3049,11 @@
         <v/>
       </c>
       <c r="S23" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="U23" s="6" t="s">
         <v>35</v>
@@ -3079,27 +3082,27 @@
         <v>92</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="7">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="H24" s="8">
-        <v>16.594000000000001</v>
+        <v>27.972000000000001</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="8">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L24" s="13" t="str">
         <f ca="1">IF(I24="DKK",1,IFERROR(_xludf.XLOOKUP(I24,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3115,7 +3118,7 @@
       </c>
       <c r="O24" s="12">
         <f t="shared" si="6"/>
-        <v>-0.27684705315174163</v>
+        <v>-7.049907049907056E-2</v>
       </c>
       <c r="P24" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3130,11 +3133,11 @@
         <v/>
       </c>
       <c r="S24" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="U24" s="6" t="s">
         <v>35</v>
@@ -3163,27 +3166,27 @@
         <v>92</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="H25" s="8">
-        <v>55.45</v>
+        <v>16.594000000000001</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="8">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="L25" s="13" t="str">
         <f ca="1">IF(I25="DKK",1,IFERROR(_xludf.XLOOKUP(I25,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3199,7 +3202,7 @@
       </c>
       <c r="O25" s="12">
         <f t="shared" si="6"/>
-        <v>-2.6149684400360695E-2</v>
+        <v>-0.27684705315174163</v>
       </c>
       <c r="P25" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3214,7 +3217,7 @@
         <v/>
       </c>
       <c r="S25" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -3247,27 +3250,27 @@
         <v>92</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H26" s="8">
-        <v>95.08</v>
+        <v>55.45</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="8">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L26" s="13" t="str">
         <f ca="1">IF(I26="DKK",1,IFERROR(_xludf.XLOOKUP(I26,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3283,7 +3286,7 @@
       </c>
       <c r="O26" s="12">
         <f t="shared" si="6"/>
-        <v>-0.2111905763567522</v>
+        <v>-2.6149684400360695E-2</v>
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3298,11 +3301,11 @@
         <v/>
       </c>
       <c r="S26" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="U26" s="6" t="s">
         <v>35</v>
@@ -3331,27 +3334,27 @@
         <v>92</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H27" s="8">
-        <v>77.56</v>
+        <v>95.08</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="8">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L27" s="13" t="str">
         <f ca="1">IF(I27="DKK",1,IFERROR(_xludf.XLOOKUP(I27,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3367,7 +3370,7 @@
       </c>
       <c r="O27" s="12">
         <f t="shared" si="6"/>
-        <v>5.6730273336771386E-3</v>
+        <v>-0.2111905763567522</v>
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3382,11 +3385,11 @@
         <v/>
       </c>
       <c r="S27" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="U27" s="6" t="s">
         <v>35</v>
@@ -3415,27 +3418,27 @@
         <v>92</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H28" s="8">
-        <v>159</v>
+        <v>77.56</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="8">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="L28" s="13" t="str">
         <f ca="1">IF(I28="DKK",1,IFERROR(_xludf.XLOOKUP(I28,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
@@ -3451,7 +3454,7 @@
       </c>
       <c r="O28" s="12">
         <f t="shared" si="6"/>
-        <v>5.6603773584905648E-2</v>
+        <v>5.6730273336771386E-3</v>
       </c>
       <c r="P28" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3466,14 +3469,14 @@
         <v/>
       </c>
       <c r="S28" s="12">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="U28" s="6" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="V28" s="10" t="b">
         <v>1</v>
@@ -3496,73 +3499,71 @@
         <v>141</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7">
-        <v>260</v>
+        <v>18</v>
       </c>
       <c r="H29" s="8">
-        <v>606</v>
+        <v>159</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J29" s="9">
-        <v>1</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="J29" s="9"/>
       <c r="K29" s="8">
-        <v>1662</v>
-      </c>
-      <c r="L29" s="13">
-        <f>IF(I29="DKK",1,IFERROR(_xludf.XLOOKUP(I29,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v>1</v>
+        <v>168</v>
+      </c>
+      <c r="L29" s="13" t="str">
+        <f ca="1">IF(I29="DKK",1,IFERROR(_xludf.XLOOKUP(I29,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v/>
       </c>
       <c r="M29" s="11">
         <f t="shared" si="0"/>
-        <v>157560</v>
-      </c>
-      <c r="N29" s="11">
-        <f t="shared" si="1"/>
-        <v>432120</v>
+        <v>0</v>
+      </c>
+      <c r="N29" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="O29" s="12">
         <f t="shared" si="6"/>
-        <v>1.7425742574257428</v>
-      </c>
-      <c r="P29" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="11">
-        <f t="shared" si="3"/>
-        <v>274560</v>
-      </c>
-      <c r="R29" s="12">
-        <f t="shared" si="4"/>
-        <v>1.7425742574257428</v>
+        <v>5.6603773584905648E-2</v>
+      </c>
+      <c r="P29" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q29" s="11" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R29" s="12" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="S29" s="12">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.5915878216036613</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="U29" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="V29" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="10" t="b">
         <v>1</v>
@@ -3577,10 +3578,96 @@
       <c r="AA29" s="14"/>
       <c r="AB29" s="14"/>
     </row>
+    <row r="30" spans="1:28">
+      <c r="A30" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F30" s="6"/>
+      <c r="G30" s="7">
+        <v>260</v>
+      </c>
+      <c r="H30" s="8">
+        <v>637</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="9">
+        <v>1</v>
+      </c>
+      <c r="K30" s="8">
+        <v>1662</v>
+      </c>
+      <c r="L30" s="13">
+        <f>IF(I30="DKK",1,IFERROR(_xludf.XLOOKUP(I30,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v>1</v>
+      </c>
+      <c r="M30" s="11">
+        <f t="shared" si="0"/>
+        <v>165620</v>
+      </c>
+      <c r="N30" s="11">
+        <f>IFERROR(G30*K30*L30,"")</f>
+        <v>432120</v>
+      </c>
+      <c r="O30" s="12">
+        <f t="shared" si="6"/>
+        <v>1.609105180533752</v>
+      </c>
+      <c r="P30" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="11">
+        <f t="shared" si="3"/>
+        <v>266500</v>
+      </c>
+      <c r="R30" s="12">
+        <f t="shared" si="4"/>
+        <v>1.609105180533752</v>
+      </c>
+      <c r="S30" s="12">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.5915878216036613</v>
+      </c>
+      <c r="T30" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="U30" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="V30" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z30" s="6"/>
+      <c r="AA30" s="14"/>
+      <c r="AB30" s="14"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="G2:S29">
+  <conditionalFormatting sqref="G2:S30">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -3594,6 +3681,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
@@ -3689,6 +3777,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
@@ -3756,7 +3845,7 @@
         <v>164</v>
       </c>
       <c r="B5" s="5">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="C5" t="s">
         <v>160</v>
@@ -3784,7 +3873,7 @@
         <v>167</v>
       </c>
       <c r="B7" s="5">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="C7" t="s">
         <v>160</v>
@@ -3861,6 +3950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
@@ -4036,7 +4126,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F29"/>
+  <sheetPr codeName="Sheet5">
+    <tabColor theme="3" tint="0.749992370372631"/>
+  </sheetPr>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
@@ -4240,10 +4333,10 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="C11" t="s">
         <v>196</v>
@@ -4260,16 +4353,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
         <v>193</v>
@@ -4280,16 +4373,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>193</v>
@@ -4300,16 +4393,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
         <v>193</v>
@@ -4320,33 +4413,36 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
         <v>193</v>
       </c>
       <c r="F15" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>94</v>
+      </c>
+      <c r="C16" t="s">
+        <v>198</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
         <v>193</v>
@@ -4357,10 +4453,10 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
@@ -4374,10 +4470,10 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="D18" t="s">
         <v>48</v>
@@ -4391,10 +4487,10 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
@@ -4408,10 +4504,10 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
         <v>48</v>
@@ -4425,10 +4521,10 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
         <v>48</v>
@@ -4442,10 +4538,10 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
@@ -4459,10 +4555,10 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
         <v>48</v>
@@ -4476,10 +4572,10 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
@@ -4493,10 +4589,10 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B25" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
@@ -4510,10 +4606,10 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B26" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
@@ -4527,10 +4623,10 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
@@ -4544,10 +4640,10 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B28" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D28" t="s">
         <v>48</v>
@@ -4561,18 +4657,52 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
         <v>193</v>
       </c>
       <c r="F29" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" t="s">
+        <v>193</v>
+      </c>
+      <c r="F30" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>142</v>
+      </c>
+      <c r="B31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" t="s">
+        <v>193</v>
+      </c>
+      <c r="F31" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4586,6 +4716,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
@@ -4618,16 +4749,16 @@
         <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>27</v>
@@ -4635,7 +4766,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="F2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -4653,6 +4784,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
@@ -4672,13 +4804,13 @@
         <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>146</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F110AF1-57B6-466D-94FB-B6048DABFA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD95FEC-F5CE-4C8A-BB39-393049E4779B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2924,10 +2924,10 @@
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7">
-        <v>154</v>
+        <v>262</v>
       </c>
       <c r="H22" s="8">
-        <v>8.6419999999999995</v>
+        <v>8.89</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>48</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O22" s="12">
         <f t="shared" si="6"/>
-        <v>-7.4288359176116536E-2</v>
+        <v>-0.1001124859392577</v>
       </c>
       <c r="P22" s="12" t="str">
         <f t="shared" ca="1" si="2"/>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD95FEC-F5CE-4C8A-BB39-393049E4779B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9ADF41-70BF-4619-8570-439030F59613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -2101,10 +2101,10 @@
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H12" s="8">
-        <v>142.44</v>
+        <v>141.49</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>48</v>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="O12" s="12">
         <f t="shared" si="6"/>
-        <v>0.10727323785453535</v>
+        <v>0.11470775319810578</v>
       </c>
       <c r="P12" s="12" t="str">
         <f t="shared" ca="1" si="2"/>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9ADF41-70BF-4619-8570-439030F59613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548B357F-022F-411E-85A4-D606FF04062F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="215">
   <si>
     <t>Asset_ID</t>
   </si>
@@ -681,6 +681,9 @@
   </si>
   <si>
     <t>4S0:XETR</t>
+  </si>
+  <si>
+    <t>4COP.DE</t>
   </si>
 </sst>
 </file>
@@ -2348,10 +2351,10 @@
         <v>93</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>94</v>
+        <v>214</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>94</v>
+        <v>214</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="7">

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548B357F-022F-411E-85A4-D606FF04062F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B83301-9D9A-4276-8929-E88D4D6FA715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1304,7 +1304,7 @@
         <v/>
       </c>
       <c r="S2" s="12">
-        <f t="shared" ref="S2:S16" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f ca="1">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1374,7 +1374,7 @@
         <v>31875</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" ref="O3:O30" si="6">IFERROR(K3/H3-1,"")</f>
+        <f t="shared" ref="O3:O30" si="5">IFERROR(K3/H3-1,"")</f>
         <v>0.46054802052785915</v>
       </c>
       <c r="P3" s="12">
@@ -1390,8 +1390,8 @@
         <v>0.46054802052785915</v>
       </c>
       <c r="S3" s="12">
-        <f t="shared" ca="1" si="5"/>
-        <v>4.3638021414460576E-2</v>
+        <f ca="1">IF(W3=TRUE,IFERROR(N3/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <v>4.4399174697693854E-2</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>43</v>
@@ -1458,7 +1458,7 @@
         <v/>
       </c>
       <c r="O4" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.38822722512118468</v>
       </c>
       <c r="P4" s="12" t="str">
@@ -1474,7 +1474,7 @@
         <v/>
       </c>
       <c r="S4" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W4=TRUE,IFERROR(N4/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -1544,7 +1544,7 @@
         <v>57742.2</v>
       </c>
       <c r="O5" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.88549160671462812</v>
       </c>
       <c r="P5" s="12">
@@ -1560,8 +1560,8 @@
         <v>0.88549160671462812</v>
       </c>
       <c r="S5" s="12">
-        <f t="shared" ca="1" si="5"/>
-        <v>7.9051148552723619E-2</v>
+        <f ca="1">IF(W5=TRUE,IFERROR(N5/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <v>8.0429992948366363E-2</v>
       </c>
       <c r="T5" s="6" t="s">
         <v>43</v>
@@ -1628,7 +1628,7 @@
         <v/>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-1.5263417035942806E-2</v>
       </c>
       <c r="P6" s="12" t="str">
@@ -1644,7 +1644,7 @@
         <v/>
       </c>
       <c r="S6" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W6=TRUE,IFERROR(N6/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -1712,7 +1712,7 @@
         <v/>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.6576234262988541E-2</v>
       </c>
       <c r="P7" s="12" t="str">
@@ -1728,7 +1728,7 @@
         <v/>
       </c>
       <c r="S7" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W7=TRUE,IFERROR(N7/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -1798,7 +1798,7 @@
         <v>57330</v>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.2431473082232301</v>
       </c>
       <c r="P8" s="12">
@@ -1814,8 +1814,8 @@
         <v>1.2431473082232301</v>
       </c>
       <c r="S8" s="12">
-        <f t="shared" ca="1" si="5"/>
-        <v>7.8486831927561562E-2</v>
+        <f ca="1">IF(W8=TRUE,IFERROR(N8/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <v>7.9855833268040424E-2</v>
       </c>
       <c r="T8" s="6" t="s">
         <v>58</v>
@@ -1884,7 +1884,7 @@
         <v>100128</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.32731376975169302</v>
       </c>
       <c r="P9" s="12">
@@ -1900,8 +1900,8 @@
         <v>-0.32731376975169302</v>
       </c>
       <c r="S9" s="12">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.13707883319802694</v>
+        <f ca="1">IF(W9=TRUE,IFERROR(N9/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <v>0.13946982161978635</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>69</v>
@@ -1943,10 +1943,10 @@
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="7">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H10" s="8">
-        <v>631.61</v>
+        <v>598.29</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>42</v>
@@ -1963,15 +1963,15 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="0"/>
-        <v>24001.18</v>
+        <v>10769.22</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>32178.399999999998</v>
+        <v>15242.4</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="6"/>
-        <v>0.34070074887984658</v>
+        <f t="shared" si="5"/>
+        <v>0.41536712965284406</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" si="2"/>
@@ -1979,15 +1979,15 @@
       </c>
       <c r="Q10" s="11">
         <f t="shared" si="3"/>
-        <v>8177.2199999999975</v>
+        <v>4473.18</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="4"/>
-        <v>0.34070074887984658</v>
+        <v>0.41536712965284406</v>
       </c>
       <c r="S10" s="12">
-        <f t="shared" ca="1" si="5"/>
-        <v>4.4053386926527945E-2</v>
+        <f ca="1">IF(W10=TRUE,IFERROR(N10/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <v>2.1231371934498158E-2</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>74</v>
@@ -2045,23 +2045,23 @@
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
       <c r="O11" s="12">
-        <f t="shared" ref="O11" si="7">IFERROR(K11/H11-1,"")</f>
+        <f t="shared" ref="O11" si="6">IFERROR(K11/H11-1,"")</f>
         <v>4.1689323907920794E-3</v>
       </c>
       <c r="P11" s="12" t="str">
-        <f t="shared" ref="P11" si="8">IFERROR(L11/J11-1,"")</f>
+        <f t="shared" ref="P11" si="7">IFERROR(L11/J11-1,"")</f>
         <v/>
       </c>
       <c r="Q11" s="11">
-        <f t="shared" ref="Q11" si="9">IFERROR(N11-M11,"")</f>
+        <f t="shared" ref="Q11" si="8">IFERROR(N11-M11,"")</f>
         <v>0</v>
       </c>
       <c r="R11" s="12" t="str">
-        <f t="shared" ref="R11" si="10">IFERROR(N11/M11-1,"")</f>
+        <f t="shared" ref="R11" si="9">IFERROR(N11/M11-1,"")</f>
         <v/>
       </c>
       <c r="S11" s="12">
-        <f t="shared" ref="S11" ca="1" si="11">IF(W11=TRUE,IFERROR(N11/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f ca="1">IF(W11=TRUE,IFERROR(N11/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.11470775319810578</v>
       </c>
       <c r="P12" s="12" t="str">
@@ -2145,7 +2145,7 @@
         <v/>
       </c>
       <c r="S12" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W12=TRUE,IFERROR(N12/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -2213,7 +2213,7 @@
         <v/>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>9.1743119266054496E-3</v>
       </c>
       <c r="P13" s="12" t="str">
@@ -2229,7 +2229,7 @@
         <v/>
       </c>
       <c r="S13" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W13=TRUE,IFERROR(N13/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -2272,10 +2272,10 @@
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="7">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="H14" s="8">
-        <v>145.84</v>
+        <v>158.22</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>42</v>
@@ -2292,15 +2292,15 @@
       </c>
       <c r="M14" s="11">
         <f>IFERROR(G14*H14*J14,"")</f>
-        <v>15750.720000000001</v>
+        <v>21043.26</v>
       </c>
       <c r="N14" s="11">
         <f t="shared" si="1"/>
-        <v>19067.400000000001</v>
+        <v>23481.15</v>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="6"/>
-        <v>0.21057323093801439</v>
+        <f t="shared" si="5"/>
+        <v>0.11585134622677296</v>
       </c>
       <c r="P14" s="12">
         <f t="shared" si="2"/>
@@ -2308,15 +2308,15 @@
       </c>
       <c r="Q14" s="11">
         <f t="shared" si="3"/>
-        <v>3316.6800000000003</v>
+        <v>2437.8900000000031</v>
       </c>
       <c r="R14" s="12">
         <f t="shared" si="4"/>
-        <v>0.21057323093801417</v>
+        <v>0.11585134622677296</v>
       </c>
       <c r="S14" s="12">
-        <f t="shared" ca="1" si="5"/>
-        <v>2.6103956377037982E-2</v>
+        <f ca="1">IF(W14=TRUE,IFERROR(N14/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <v>3.2707252735772678E-2</v>
       </c>
       <c r="T14" s="6" t="s">
         <v>90</v>
@@ -2383,7 +2383,7 @@
         <v/>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-2.0270270270270285E-2</v>
       </c>
       <c r="P15" s="12" t="str">
@@ -2399,7 +2399,7 @@
         <v/>
       </c>
       <c r="S15" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W15=TRUE,IFERROR(N15/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T15" s="6" t="s">
@@ -2469,7 +2469,7 @@
         <v/>
       </c>
       <c r="O16" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.3325810237429021E-2</v>
       </c>
       <c r="P16" s="12" t="str">
@@ -2485,7 +2485,7 @@
         <v/>
       </c>
       <c r="S16" s="12">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(W16=TRUE,IFERROR(N16/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -2518,41 +2518,62 @@
         <v>92</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>207</v>
+        <v>101</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>208</v>
+        <v>102</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>209</v>
+        <v>102</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="7">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H17" s="8">
-        <v>78.83</v>
+        <v>28.96</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="8">
-        <v>79</v>
-      </c>
-      <c r="L17" s="13"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="L17" s="13" t="str">
+        <f ca="1">IF(I17="DKK",1,IFERROR(_xludf.XLOOKUP(I17,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
+        <v/>
+      </c>
+      <c r="M17" s="11">
+        <f>IFERROR(G17*H17*J17,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="11" t="str">
+        <f ca="1">IFERROR(G17*K17*L17,"")</f>
+        <v/>
+      </c>
       <c r="O17" s="12">
-        <f t="shared" si="6"/>
-        <v>2.1565393885576434E-3</v>
-      </c>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
+        <f>IFERROR(K17/H17-1,"")</f>
+        <v>-0.20580110497237569</v>
+      </c>
+      <c r="P17" s="12" t="str">
+        <f ca="1">IFERROR(L17/J17-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="11" t="str">
+        <f ca="1">IFERROR(N17-M17,"")</f>
+        <v/>
+      </c>
+      <c r="R17" s="12" t="str">
+        <f ca="1">IFERROR(N17/M17-1,"")</f>
+        <v/>
+      </c>
+      <c r="S17" s="12">
+        <f ca="1">IF(W17=TRUE,IFERROR(N17/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <v>0</v>
+      </c>
       <c r="T17" s="6" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="U17" s="6" t="s">
         <v>35</v>
@@ -2581,62 +2602,41 @@
         <v>92</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>102</v>
+        <v>209</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="7">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="H18" s="8">
-        <v>28.96</v>
+        <v>78.83</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="8">
-        <v>23</v>
-      </c>
-      <c r="L18" s="13" t="str">
-        <f ca="1">IF(I18="DKK",1,IFERROR(_xludf.XLOOKUP(I18,FX!$A$2:$A$20,FX!$B$2:$B$20,""),""))</f>
-        <v/>
-      </c>
-      <c r="M18" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="L18" s="13"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
       <c r="O18" s="12">
-        <f t="shared" si="6"/>
-        <v>-0.20580110497237569</v>
-      </c>
-      <c r="P18" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="Q18" s="11" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="R18" s="12" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S18" s="12">
-        <f t="shared" ref="S18:S30" ca="1" si="12">IF(W18=TRUE,IFERROR(N18/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>2.1565393885576434E-3</v>
+      </c>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
       <c r="T18" s="6" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="U18" s="6" t="s">
         <v>35</v>
@@ -2700,7 +2700,7 @@
         <v/>
       </c>
       <c r="O19" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.12445867068348704</v>
       </c>
       <c r="P19" s="12" t="str">
@@ -2716,7 +2716,7 @@
         <v/>
       </c>
       <c r="S19" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W19=TRUE,IFERROR(N19/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T19" s="6" t="s">
@@ -2784,7 +2784,7 @@
         <v/>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="P20" s="12" t="str">
@@ -2800,7 +2800,7 @@
         <v/>
       </c>
       <c r="S20" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -2843,10 +2843,10 @@
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H21" s="8">
-        <v>114.15900000000001</v>
+        <v>108.26</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>48</v>
@@ -2868,8 +2868,8 @@
         <v/>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="6"/>
-        <v>-8.0230205240059971E-2</v>
+        <f t="shared" si="5"/>
+        <v>-3.0112691668206182E-2</v>
       </c>
       <c r="P21" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2884,7 +2884,7 @@
         <v/>
       </c>
       <c r="S21" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W21=TRUE,IFERROR(N21/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -2952,7 +2952,7 @@
         <v/>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.1001124859392577</v>
       </c>
       <c r="P22" s="12" t="str">
@@ -2968,7 +2968,7 @@
         <v/>
       </c>
       <c r="S22" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W22=TRUE,IFERROR(N22/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -3036,7 +3036,7 @@
         <v/>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-1.5817223198594021E-2</v>
       </c>
       <c r="P23" s="12" t="str">
@@ -3052,7 +3052,7 @@
         <v/>
       </c>
       <c r="S23" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W23=TRUE,IFERROR(N23/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -3120,7 +3120,7 @@
         <v/>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-7.049907049907056E-2</v>
       </c>
       <c r="P24" s="12" t="str">
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="S24" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W24=TRUE,IFERROR(N24/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -3204,7 +3204,7 @@
         <v/>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.27684705315174163</v>
       </c>
       <c r="P25" s="12" t="str">
@@ -3220,7 +3220,7 @@
         <v/>
       </c>
       <c r="S25" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W25=TRUE,IFERROR(N25/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -3263,10 +3263,10 @@
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H26" s="8">
-        <v>55.45</v>
+        <v>56.86</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>48</v>
@@ -3288,8 +3288,8 @@
         <v/>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="6"/>
-        <v>-2.6149684400360695E-2</v>
+        <f t="shared" si="5"/>
+        <v>-5.0298979950756273E-2</v>
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3304,7 +3304,7 @@
         <v/>
       </c>
       <c r="S26" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W26=TRUE,IFERROR(N26/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-0.2111905763567522</v>
       </c>
       <c r="P27" s="12" t="str">
@@ -3388,7 +3388,7 @@
         <v/>
       </c>
       <c r="S27" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W27=TRUE,IFERROR(N27/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.6730273336771386E-3</v>
       </c>
       <c r="P28" s="12" t="str">
@@ -3472,7 +3472,7 @@
         <v/>
       </c>
       <c r="S28" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W28=TRUE,IFERROR(N28/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -3540,7 +3540,7 @@
         <v/>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.6603773584905648E-2</v>
       </c>
       <c r="P29" s="12" t="str">
@@ -3556,7 +3556,7 @@
         <v/>
       </c>
       <c r="S29" s="12">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(W29=TRUE,IFERROR(N29/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
@@ -3626,7 +3626,7 @@
         <v>432120</v>
       </c>
       <c r="O30" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.609105180533752</v>
       </c>
       <c r="P30" s="12">
@@ -3642,8 +3642,8 @@
         <v>1.609105180533752</v>
       </c>
       <c r="S30" s="12">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.5915878216036613</v>
+        <f ca="1">IF(W30=TRUE,IFERROR(N30/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <v>0.60190655279584215</v>
       </c>
       <c r="T30" s="6" t="s">
         <v>58</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B83301-9D9A-4276-8929-E88D4D6FA715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88787A36-6A58-4047-9F90-CD26617DEB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="218">
   <si>
     <t>Asset_ID</t>
   </si>
@@ -323,9 +323,6 @@
     <t>Global X Copper Miners UCITS ETF</t>
   </si>
   <si>
-    <t>COPX.L</t>
-  </si>
-  <si>
     <t>Materialer</t>
   </si>
   <si>
@@ -635,9 +632,6 @@
     <t>XNYS</t>
   </si>
   <si>
-    <t>XLON</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -684,6 +678,21 @@
   </si>
   <si>
     <t>4COP.DE</t>
+  </si>
+  <si>
+    <t>Astera Labs</t>
+  </si>
+  <si>
+    <t>ALAB</t>
+  </si>
+  <si>
+    <t>64B.DE</t>
+  </si>
+  <si>
+    <t>Celestica</t>
+  </si>
+  <si>
+    <t>CLS</t>
   </si>
 </sst>
 </file>
@@ -942,7 +951,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="WatchlistTable" displayName="WatchlistTable" ref="A1:J2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="WatchlistTable" displayName="WatchlistTable" ref="A1:J3">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Ticker"/>
@@ -1304,7 +1313,7 @@
         <v/>
       </c>
       <c r="S2" s="12">
-        <f ca="1">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ref="S2:S17" ca="1" si="5">IF(W2=TRUE,IFERROR(N2/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1374,7 +1383,7 @@
         <v>31875</v>
       </c>
       <c r="O3" s="12">
-        <f t="shared" ref="O3:O30" si="5">IFERROR(K3/H3-1,"")</f>
+        <f t="shared" ref="O3:O30" si="6">IFERROR(K3/H3-1,"")</f>
         <v>0.46054802052785915</v>
       </c>
       <c r="P3" s="12">
@@ -1390,7 +1399,7 @@
         <v>0.46054802052785915</v>
       </c>
       <c r="S3" s="12">
-        <f ca="1">IF(W3=TRUE,IFERROR(N3/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>4.4399174697693854E-2</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -1458,7 +1467,7 @@
         <v/>
       </c>
       <c r="O4" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.38822722512118468</v>
       </c>
       <c r="P4" s="12" t="str">
@@ -1474,7 +1483,7 @@
         <v/>
       </c>
       <c r="S4" s="12">
-        <f ca="1">IF(W4=TRUE,IFERROR(N4/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -1544,7 +1553,7 @@
         <v>57742.2</v>
       </c>
       <c r="O5" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.88549160671462812</v>
       </c>
       <c r="P5" s="12">
@@ -1560,7 +1569,7 @@
         <v>0.88549160671462812</v>
       </c>
       <c r="S5" s="12">
-        <f ca="1">IF(W5=TRUE,IFERROR(N5/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>8.0429992948366363E-2</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -1628,7 +1637,7 @@
         <v/>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.5263417035942806E-2</v>
       </c>
       <c r="P6" s="12" t="str">
@@ -1644,7 +1653,7 @@
         <v/>
       </c>
       <c r="S6" s="12">
-        <f ca="1">IF(W6=TRUE,IFERROR(N6/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -1712,7 +1721,7 @@
         <v/>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.6576234262988541E-2</v>
       </c>
       <c r="P7" s="12" t="str">
@@ -1728,7 +1737,7 @@
         <v/>
       </c>
       <c r="S7" s="12">
-        <f ca="1">IF(W7=TRUE,IFERROR(N7/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -1798,7 +1807,7 @@
         <v>57330</v>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.2431473082232301</v>
       </c>
       <c r="P8" s="12">
@@ -1814,7 +1823,7 @@
         <v>1.2431473082232301</v>
       </c>
       <c r="S8" s="12">
-        <f ca="1">IF(W8=TRUE,IFERROR(N8/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>7.9855833268040424E-2</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -1884,7 +1893,7 @@
         <v>100128</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.32731376975169302</v>
       </c>
       <c r="P9" s="12">
@@ -1900,7 +1909,7 @@
         <v>-0.32731376975169302</v>
       </c>
       <c r="S9" s="12">
-        <f ca="1">IF(W9=TRUE,IFERROR(N9/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0.13946982161978635</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -1970,7 +1979,7 @@
         <v>15242.4</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.41536712965284406</v>
       </c>
       <c r="P10" s="12">
@@ -1986,7 +1995,7 @@
         <v>0.41536712965284406</v>
       </c>
       <c r="S10" s="12">
-        <f ca="1">IF(W10=TRUE,IFERROR(N10/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>2.1231371934498158E-2</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -2019,13 +2028,13 @@
         <v>29</v>
       </c>
       <c r="C11" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>213</v>
-      </c>
       <c r="E11" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7">
@@ -2045,23 +2054,23 @@
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
       <c r="O11" s="12">
-        <f t="shared" ref="O11" si="6">IFERROR(K11/H11-1,"")</f>
+        <f t="shared" ref="O11" si="7">IFERROR(K11/H11-1,"")</f>
         <v>4.1689323907920794E-3</v>
       </c>
       <c r="P11" s="12" t="str">
-        <f t="shared" ref="P11" si="7">IFERROR(L11/J11-1,"")</f>
+        <f t="shared" ref="P11" si="8">IFERROR(L11/J11-1,"")</f>
         <v/>
       </c>
       <c r="Q11" s="11">
-        <f t="shared" ref="Q11" si="8">IFERROR(N11-M11,"")</f>
+        <f t="shared" ref="Q11" si="9">IFERROR(N11-M11,"")</f>
         <v>0</v>
       </c>
       <c r="R11" s="12" t="str">
-        <f t="shared" ref="R11" si="9">IFERROR(N11/M11-1,"")</f>
+        <f t="shared" ref="R11" si="10">IFERROR(N11/M11-1,"")</f>
         <v/>
       </c>
       <c r="S11" s="12">
-        <f ca="1">IF(W11=TRUE,IFERROR(N11/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -2129,7 +2138,7 @@
         <v/>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.11470775319810578</v>
       </c>
       <c r="P12" s="12" t="str">
@@ -2145,7 +2154,7 @@
         <v/>
       </c>
       <c r="S12" s="12">
-        <f ca="1">IF(W12=TRUE,IFERROR(N12/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -2213,7 +2222,7 @@
         <v/>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.1743119266054496E-3</v>
       </c>
       <c r="P13" s="12" t="str">
@@ -2229,7 +2238,7 @@
         <v/>
       </c>
       <c r="S13" s="12">
-        <f ca="1">IF(W13=TRUE,IFERROR(N13/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -2299,7 +2308,7 @@
         <v>23481.15</v>
       </c>
       <c r="O14" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.11585134622677296</v>
       </c>
       <c r="P14" s="12">
@@ -2315,7 +2324,7 @@
         <v>0.11585134622677296</v>
       </c>
       <c r="S14" s="12">
-        <f ca="1">IF(W14=TRUE,IFERROR(N14/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>3.2707252735772678E-2</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -2351,17 +2360,17 @@
         <v>93</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="7">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H15" s="8">
-        <v>59.2</v>
+        <v>57.93</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>57</v>
@@ -2383,8 +2392,8 @@
         <v/>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="5"/>
-        <v>-2.0270270270270285E-2</v>
+        <f t="shared" si="6"/>
+        <v>1.2083549110997183E-3</v>
       </c>
       <c r="P15" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2399,11 +2408,11 @@
         <v/>
       </c>
       <c r="S15" s="12">
-        <f ca="1">IF(W15=TRUE,IFERROR(N15/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U15" s="6" t="s">
         <v>35</v>
@@ -2422,32 +2431,32 @@
       </c>
       <c r="Z15" s="6"/>
       <c r="AA15" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AB15" s="14"/>
     </row>
     <row r="16" spans="1:28">
       <c r="A16" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C16" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="E16" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="7">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="H16" s="8">
-        <v>44.308</v>
+        <v>46.039000000000001</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>48</v>
@@ -2469,8 +2478,8 @@
         <v/>
       </c>
       <c r="O16" s="12">
-        <f t="shared" si="5"/>
-        <v>8.3325810237429021E-2</v>
+        <f t="shared" si="6"/>
+        <v>4.2594322205086854E-2</v>
       </c>
       <c r="P16" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2485,7 +2494,7 @@
         <v/>
       </c>
       <c r="S16" s="12">
-        <f ca="1">IF(W16=TRUE,IFERROR(N16/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -2512,19 +2521,19 @@
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C17" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>102</v>
-      </c>
       <c r="E17" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="7">
@@ -2569,7 +2578,7 @@
         <v/>
       </c>
       <c r="S17" s="12">
-        <f ca="1">IF(W17=TRUE,IFERROR(N17/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -2596,19 +2605,19 @@
     </row>
     <row r="18" spans="1:28">
       <c r="A18" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C18" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="7">
@@ -2628,7 +2637,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.1565393885576434E-3</v>
       </c>
       <c r="P18" s="12"/>
@@ -2636,7 +2645,7 @@
       <c r="R18" s="12"/>
       <c r="S18" s="12"/>
       <c r="T18" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="U18" s="6" t="s">
         <v>35</v>
@@ -2659,19 +2668,19 @@
     </row>
     <row r="19" spans="1:28">
       <c r="A19" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C19" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>105</v>
-      </c>
       <c r="E19" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7">
@@ -2700,7 +2709,7 @@
         <v/>
       </c>
       <c r="O19" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.12445867068348704</v>
       </c>
       <c r="P19" s="12" t="str">
@@ -2716,7 +2725,7 @@
         <v/>
       </c>
       <c r="S19" s="12">
-        <f ca="1">IF(W19=TRUE,IFERROR(N19/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ref="S19:S30" ca="1" si="11">IF(W19=TRUE,IFERROR(N19/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T19" s="6" t="s">
@@ -2743,26 +2752,26 @@
     </row>
     <row r="20" spans="1:28">
       <c r="A20" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C20" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>108</v>
-      </c>
       <c r="E20" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="7">
         <v>363</v>
       </c>
       <c r="H20" s="8">
-        <v>9</v>
+        <v>9.9689999999999994</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>48</v>
@@ -2784,8 +2793,8 @@
         <v/>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="5"/>
-        <v>0.88888888888888884</v>
+        <f t="shared" si="6"/>
+        <v>0.70528638780218689</v>
       </c>
       <c r="P20" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2800,7 +2809,7 @@
         <v/>
       </c>
       <c r="S20" s="12">
-        <f ca="1">IF(W20=TRUE,IFERROR(N20/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -2827,19 +2836,19 @@
     </row>
     <row r="21" spans="1:28">
       <c r="A21" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C21" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>111</v>
-      </c>
       <c r="E21" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="7">
@@ -2868,7 +2877,7 @@
         <v/>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-3.0112691668206182E-2</v>
       </c>
       <c r="P21" s="12" t="str">
@@ -2884,7 +2893,7 @@
         <v/>
       </c>
       <c r="S21" s="12">
-        <f ca="1">IF(W21=TRUE,IFERROR(N21/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -2911,19 +2920,19 @@
     </row>
     <row r="22" spans="1:28">
       <c r="A22" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C22" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>114</v>
-      </c>
       <c r="E22" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7">
@@ -2952,7 +2961,7 @@
         <v/>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.1001124859392577</v>
       </c>
       <c r="P22" s="12" t="str">
@@ -2968,11 +2977,11 @@
         <v/>
       </c>
       <c r="S22" s="12">
-        <f ca="1">IF(W22=TRUE,IFERROR(N22/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="U22" s="6" t="s">
         <v>35</v>
@@ -2995,19 +3004,19 @@
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C23" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>118</v>
-      </c>
       <c r="E23" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7">
@@ -3036,7 +3045,7 @@
         <v/>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.5817223198594021E-2</v>
       </c>
       <c r="P23" s="12" t="str">
@@ -3052,11 +3061,11 @@
         <v/>
       </c>
       <c r="S23" s="12">
-        <f ca="1">IF(W23=TRUE,IFERROR(N23/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U23" s="6" t="s">
         <v>35</v>
@@ -3079,19 +3088,19 @@
     </row>
     <row r="24" spans="1:28">
       <c r="A24" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C24" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>122</v>
-      </c>
       <c r="E24" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="7">
@@ -3120,7 +3129,7 @@
         <v/>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-7.049907049907056E-2</v>
       </c>
       <c r="P24" s="12" t="str">
@@ -3136,7 +3145,7 @@
         <v/>
       </c>
       <c r="S24" s="12">
-        <f ca="1">IF(W24=TRUE,IFERROR(N24/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -3163,19 +3172,19 @@
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C25" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="E25" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7">
@@ -3204,7 +3213,7 @@
         <v/>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.27684705315174163</v>
       </c>
       <c r="P25" s="12" t="str">
@@ -3220,11 +3229,11 @@
         <v/>
       </c>
       <c r="S25" s="12">
-        <f ca="1">IF(W25=TRUE,IFERROR(N25/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U25" s="6" t="s">
         <v>35</v>
@@ -3247,19 +3256,19 @@
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C26" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="E26" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7">
@@ -3288,7 +3297,7 @@
         <v/>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-5.0298979950756273E-2</v>
       </c>
       <c r="P26" s="12" t="str">
@@ -3304,11 +3313,11 @@
         <v/>
       </c>
       <c r="S26" s="12">
-        <f ca="1">IF(W26=TRUE,IFERROR(N26/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U26" s="6" t="s">
         <v>35</v>
@@ -3331,19 +3340,19 @@
     </row>
     <row r="27" spans="1:28">
       <c r="A27" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C27" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>131</v>
-      </c>
       <c r="E27" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7">
@@ -3372,7 +3381,7 @@
         <v/>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.2111905763567522</v>
       </c>
       <c r="P27" s="12" t="str">
@@ -3388,11 +3397,11 @@
         <v/>
       </c>
       <c r="S27" s="12">
-        <f ca="1">IF(W27=TRUE,IFERROR(N27/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="U27" s="6" t="s">
         <v>35</v>
@@ -3415,19 +3424,19 @@
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C28" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>135</v>
-      </c>
       <c r="E28" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7">
@@ -3456,7 +3465,7 @@
         <v/>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.6730273336771386E-3</v>
       </c>
       <c r="P28" s="12" t="str">
@@ -3472,7 +3481,7 @@
         <v/>
       </c>
       <c r="S28" s="12">
-        <f ca="1">IF(W28=TRUE,IFERROR(N28/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -3499,19 +3508,19 @@
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C29" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="E29" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7">
@@ -3540,7 +3549,7 @@
         <v/>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.6603773584905648E-2</v>
       </c>
       <c r="P29" s="12" t="str">
@@ -3556,14 +3565,14 @@
         <v/>
       </c>
       <c r="S29" s="12">
-        <f ca="1">IF(W29=TRUE,IFERROR(N29/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="U29" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="U29" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="V29" s="10" t="b">
         <v>1</v>
@@ -3583,19 +3592,19 @@
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7">
@@ -3626,7 +3635,7 @@
         <v>432120</v>
       </c>
       <c r="O30" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.609105180533752</v>
       </c>
       <c r="P30" s="12">
@@ -3642,14 +3651,14 @@
         <v>1.609105180533752</v>
       </c>
       <c r="S30" s="12">
-        <f ca="1">IF(W30=TRUE,IFERROR(N30/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ca="1" si="11"/>
         <v>0.60190655279584215</v>
       </c>
       <c r="T30" s="6" t="s">
         <v>58</v>
       </c>
       <c r="U30" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="V30" s="10" t="b">
         <v>0</v>
@@ -3701,16 +3710,16 @@
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>27</v>
@@ -3721,7 +3730,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
@@ -3735,13 +3744,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D3" s="1" t="b">
         <v>1</v>
@@ -3752,22 +3761,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" t="s">
         <v>149</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>150</v>
-      </c>
-      <c r="D4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3792,150 +3801,150 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" t="s">
         <v>156</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>157</v>
-      </c>
-      <c r="D2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B3" s="5">
         <v>0.02</v>
       </c>
       <c r="C3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" t="s">
         <v>160</v>
-      </c>
-      <c r="D3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B4" s="5">
         <v>0.14000000000000001</v>
       </c>
       <c r="C4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="5">
         <v>0.25</v>
       </c>
       <c r="C5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B6" s="5">
         <v>0.25</v>
       </c>
       <c r="C6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B7" s="5">
         <v>0.2</v>
       </c>
       <c r="C7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B8" s="5">
         <v>0.2</v>
       </c>
       <c r="C8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B9" s="5">
         <v>0.1</v>
       </c>
       <c r="C9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" t="s">
         <v>170</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
         <v>171</v>
-      </c>
-      <c r="D10" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" t="s">
         <v>174</v>
-      </c>
-      <c r="D11" t="s">
-        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3974,19 +3983,19 @@
         <v>11</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3997,16 +4006,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
         <v>181</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4015,13 +4024,13 @@
       </c>
       <c r="B3" s="3"/>
       <c r="D3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
         <v>183</v>
-      </c>
-      <c r="F3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4030,13 +4039,13 @@
       </c>
       <c r="B4" s="3"/>
       <c r="D4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
         <v>183</v>
-      </c>
-      <c r="F4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4045,73 +4054,73 @@
       </c>
       <c r="B5" s="3"/>
       <c r="D5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
         <v>183</v>
-      </c>
-      <c r="F5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B6" s="3"/>
       <c r="D6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
         <v>183</v>
-      </c>
-      <c r="F6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B7" s="3"/>
       <c r="D7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
         <v>183</v>
-      </c>
-      <c r="F7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B8" s="3"/>
       <c r="D8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
         <v>183</v>
-      </c>
-      <c r="F8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B9" s="3"/>
       <c r="D9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
         <v>183</v>
-      </c>
-      <c r="F9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -4151,16 +4160,16 @@
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4171,16 +4180,16 @@
         <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4191,16 +4200,16 @@
         <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D3" t="s">
         <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4211,16 +4220,16 @@
         <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D4" t="s">
         <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4231,16 +4240,16 @@
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D5" t="s">
         <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4254,10 +4263,10 @@
         <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4268,16 +4277,16 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D7" t="s">
         <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4291,10 +4300,10 @@
         <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4308,10 +4317,10 @@
         <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4322,36 +4331,36 @@
         <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D10" t="s">
         <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D11" t="s">
         <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4362,16 +4371,16 @@
         <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D12" t="s">
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4382,16 +4391,16 @@
         <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D13" t="s">
         <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4402,16 +4411,16 @@
         <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D14" t="s">
         <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4422,291 +4431,291 @@
         <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D15" t="s">
         <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="C16" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D18" t="s">
         <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
         <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
         <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
         <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F27" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
         <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
         <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
         <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D31" t="s">
         <v>42</v>
       </c>
       <c r="E31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -4720,10 +4729,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.4140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
@@ -4752,35 +4761,77 @@
         <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2" t="s">
+        <v>48</v>
+      </c>
       <c r="F2" t="s">
-        <v>203</v>
+        <v>201</v>
+      </c>
+      <c r="I2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G3">
+        <v>290</v>
+      </c>
+      <c r="H3">
+        <v>375</v>
+      </c>
+      <c r="I3">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:I200">
+  <conditionalFormatting sqref="G2:I201">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4807,19 +4858,19 @@
         <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="F1" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4830,14 +4881,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>50000</v>
+        <v>80629</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>50000</v>
+        <v>80629</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88787A36-6A58-4047-9F90-CD26617DEB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{A06B6B76-783C-4E39-AA92-5BDAD4811C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Cash" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="220">
   <si>
     <t>Asset_ID</t>
   </si>
@@ -693,6 +694,12 @@
   </si>
   <si>
     <t>CLS</t>
+  </si>
+  <si>
+    <t>Part of SEC0 0,49%</t>
+  </si>
+  <si>
+    <t>Entry 295$, FV 365$, support 260$</t>
   </si>
 </sst>
 </file>
@@ -2054,19 +2061,19 @@
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
       <c r="O11" s="12">
-        <f t="shared" ref="O11" si="7">IFERROR(K11/H11-1,"")</f>
+        <f>IFERROR(K11/H11-1,"")</f>
         <v>4.1689323907920794E-3</v>
       </c>
       <c r="P11" s="12" t="str">
-        <f t="shared" ref="P11" si="8">IFERROR(L11/J11-1,"")</f>
+        <f>IFERROR(L11/J11-1,"")</f>
         <v/>
       </c>
       <c r="Q11" s="11">
-        <f t="shared" ref="Q11" si="9">IFERROR(N11-M11,"")</f>
+        <f>IFERROR(N11-M11,"")</f>
         <v>0</v>
       </c>
       <c r="R11" s="12" t="str">
-        <f t="shared" ref="R11" si="10">IFERROR(N11/M11-1,"")</f>
+        <f>IFERROR(N11/M11-1,"")</f>
         <v/>
       </c>
       <c r="S11" s="12">
@@ -2725,7 +2732,7 @@
         <v/>
       </c>
       <c r="S19" s="12">
-        <f t="shared" ref="S19:S30" ca="1" si="11">IF(W19=TRUE,IFERROR(N19/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
+        <f t="shared" ref="S19:S30" ca="1" si="7">IF(W19=TRUE,IFERROR(N19/SUMIFS($N$2:$N$501,$W$2:$W$501,TRUE),0),0)</f>
         <v>0</v>
       </c>
       <c r="T19" s="6" t="s">
@@ -2809,7 +2816,7 @@
         <v/>
       </c>
       <c r="S20" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -2893,7 +2900,7 @@
         <v/>
       </c>
       <c r="S21" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -2977,7 +2984,7 @@
         <v/>
       </c>
       <c r="S22" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -3061,7 +3068,7 @@
         <v/>
       </c>
       <c r="S23" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -3145,7 +3152,7 @@
         <v/>
       </c>
       <c r="S24" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -3229,7 +3236,7 @@
         <v/>
       </c>
       <c r="S25" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -3313,7 +3320,7 @@
         <v/>
       </c>
       <c r="S26" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -3397,7 +3404,7 @@
         <v/>
       </c>
       <c r="S27" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -3481,7 +3488,7 @@
         <v/>
       </c>
       <c r="S28" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -3565,7 +3572,7 @@
         <v/>
       </c>
       <c r="S29" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
@@ -3651,7 +3658,7 @@
         <v>1.609105180533752</v>
       </c>
       <c r="S30" s="12">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0.60190655279584215</v>
       </c>
       <c r="T30" s="6" t="s">
@@ -3969,7 +3976,7 @@
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.08203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.75" customWidth="1"/>
     <col min="5" max="5" width="15.58203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
@@ -4732,16 +4739,15 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.4140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="8.5" customWidth="1"/>
     <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.08203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="6" width="13.25" customWidth="1"/>
+    <col min="7" max="8" width="12.1640625" customWidth="1"/>
     <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.08203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4789,11 +4795,14 @@
       <c r="D2" t="s">
         <v>48</v>
       </c>
-      <c r="F2" t="s">
-        <v>201</v>
+      <c r="E2" t="s">
+        <v>49</v>
       </c>
       <c r="I2">
         <v>94</v>
+      </c>
+      <c r="J2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4809,6 +4818,9 @@
       <c r="D3" t="s">
         <v>57</v>
       </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
       <c r="F3" t="s">
         <v>201</v>
       </c>
@@ -4816,10 +4828,13 @@
         <v>290</v>
       </c>
       <c r="H3">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="I3">
         <v>91</v>
+      </c>
+      <c r="J3" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{A06B6B76-783C-4E39-AA92-5BDAD4811C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98676285-BA67-4D03-87F5-5A0110A434F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,6 @@
     <sheet name="Cash" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1282,7 +1281,7 @@
         <v>47</v>
       </c>
       <c r="H2" s="8">
-        <v>858.39</v>
+        <v>859.66</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>33</v>
@@ -1305,7 +1304,7 @@
       </c>
       <c r="O2" s="12">
         <f>IFERROR(K2/H2-1,"")</f>
-        <v>0.13468237048427878</v>
+        <v>0.13300607216806659</v>
       </c>
       <c r="P2" s="12" t="str">
         <f t="shared" ref="P2:P30" ca="1" si="2">IFERROR(L2/J2-1,"")</f>
@@ -1366,7 +1365,7 @@
         <v>50</v>
       </c>
       <c r="H3" s="8">
-        <v>436.48</v>
+        <v>437.67</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>42</v>
@@ -1383,7 +1382,7 @@
       </c>
       <c r="M3" s="11">
         <f t="shared" si="0"/>
-        <v>21824</v>
+        <v>21883.5</v>
       </c>
       <c r="N3" s="11">
         <f t="shared" si="1"/>
@@ -1391,7 +1390,7 @@
       </c>
       <c r="O3" s="12">
         <f t="shared" ref="O3:O30" si="6">IFERROR(K3/H3-1,"")</f>
-        <v>0.46054802052785915</v>
+        <v>0.45657687298649652</v>
       </c>
       <c r="P3" s="12">
         <f t="shared" si="2"/>
@@ -1399,11 +1398,11 @@
       </c>
       <c r="Q3" s="11">
         <f t="shared" si="3"/>
-        <v>10051</v>
+        <v>9991.5</v>
       </c>
       <c r="R3" s="12">
         <f t="shared" si="4"/>
-        <v>0.46054802052785915</v>
+        <v>0.45657687298649674</v>
       </c>
       <c r="S3" s="12">
         <f t="shared" ca="1" si="5"/>
@@ -1452,7 +1451,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="8">
-        <v>1078.93</v>
+        <v>1080.49</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>48</v>
@@ -1475,7 +1474,7 @@
       </c>
       <c r="O4" s="12">
         <f t="shared" si="6"/>
-        <v>0.38822722512118468</v>
+        <v>0.38622291738007752</v>
       </c>
       <c r="P4" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1536,7 +1535,7 @@
         <v>153</v>
       </c>
       <c r="H5" s="8">
-        <v>200.16</v>
+        <v>200.43</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>42</v>
@@ -1553,7 +1552,7 @@
       </c>
       <c r="M5" s="11">
         <f t="shared" si="0"/>
-        <v>30624.48</v>
+        <v>30665.79</v>
       </c>
       <c r="N5" s="11">
         <f t="shared" si="1"/>
@@ -1561,7 +1560,7 @@
       </c>
       <c r="O5" s="12">
         <f t="shared" si="6"/>
-        <v>0.88549160671462812</v>
+        <v>0.88295165394402009</v>
       </c>
       <c r="P5" s="12">
         <f t="shared" si="2"/>
@@ -1569,11 +1568,11 @@
       </c>
       <c r="Q5" s="11">
         <f t="shared" si="3"/>
-        <v>27117.719999999998</v>
+        <v>27076.409999999996</v>
       </c>
       <c r="R5" s="12">
         <f t="shared" si="4"/>
-        <v>0.88549160671462812</v>
+        <v>0.88295165394402031</v>
       </c>
       <c r="S5" s="12">
         <f t="shared" ca="1" si="5"/>
@@ -1619,10 +1618,10 @@
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="7">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H6" s="8">
-        <v>40.619999999999997</v>
+        <v>42.62</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>57</v>
@@ -1645,7 +1644,7 @@
       </c>
       <c r="O6" s="12">
         <f t="shared" si="6"/>
-        <v>-1.5263417035942806E-2</v>
+        <v>-6.1473486625997165E-2</v>
       </c>
       <c r="P6" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1706,7 +1705,7 @@
         <v>16</v>
       </c>
       <c r="H7" s="8">
-        <v>394.77</v>
+        <v>396.46</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>48</v>
@@ -1729,7 +1728,7 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="6"/>
-        <v>7.6576234262988541E-2</v>
+        <v>7.1987085708520526E-2</v>
       </c>
       <c r="P7" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1790,7 +1789,7 @@
         <v>63</v>
       </c>
       <c r="H8" s="8">
-        <v>405.68</v>
+        <v>406.95</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>42</v>
@@ -1807,7 +1806,7 @@
       </c>
       <c r="M8" s="11">
         <f t="shared" si="0"/>
-        <v>25557.84</v>
+        <v>25637.85</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" si="1"/>
@@ -1815,7 +1814,7 @@
       </c>
       <c r="O8" s="12">
         <f t="shared" si="6"/>
-        <v>1.2431473082232301</v>
+        <v>1.2361469467993613</v>
       </c>
       <c r="P8" s="12">
         <f t="shared" si="2"/>
@@ -1823,11 +1822,11 @@
       </c>
       <c r="Q8" s="11">
         <f t="shared" si="3"/>
-        <v>31772.16</v>
+        <v>31692.15</v>
       </c>
       <c r="R8" s="12">
         <f t="shared" si="4"/>
-        <v>1.2431473082232301</v>
+        <v>1.2361469467993613</v>
       </c>
       <c r="S8" s="12">
         <f t="shared" ca="1" si="5"/>
@@ -1962,7 +1961,7 @@
         <v>18</v>
       </c>
       <c r="H10" s="8">
-        <v>598.29</v>
+        <v>599.5</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>42</v>
@@ -1979,7 +1978,7 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="0"/>
-        <v>10769.22</v>
+        <v>10791</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
@@ -1987,7 +1986,7 @@
       </c>
       <c r="O10" s="12">
         <f t="shared" si="6"/>
-        <v>0.41536712965284406</v>
+        <v>0.41251042535446203</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" si="2"/>
@@ -1995,11 +1994,11 @@
       </c>
       <c r="Q10" s="11">
         <f t="shared" si="3"/>
-        <v>4473.18</v>
+        <v>4451.3999999999996</v>
       </c>
       <c r="R10" s="12">
         <f t="shared" si="4"/>
-        <v>0.41536712965284406</v>
+        <v>0.41251042535446203</v>
       </c>
       <c r="S10" s="12">
         <f t="shared" ca="1" si="5"/>
@@ -2048,7 +2047,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="8">
-        <v>110.34</v>
+        <v>110.64</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>48</v>
@@ -2062,7 +2061,7 @@
       <c r="N11" s="11"/>
       <c r="O11" s="12">
         <f>IFERROR(K11/H11-1,"")</f>
-        <v>4.1689323907920794E-3</v>
+        <v>1.4461315979754641E-3</v>
       </c>
       <c r="P11" s="12" t="str">
         <f>IFERROR(L11/J11-1,"")</f>
@@ -2123,7 +2122,7 @@
         <v>10</v>
       </c>
       <c r="H12" s="8">
-        <v>141.49</v>
+        <v>142.09</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>48</v>
@@ -2146,7 +2145,7 @@
       </c>
       <c r="O12" s="12">
         <f t="shared" si="6"/>
-        <v>0.11470775319810578</v>
+        <v>0.11000070377929472</v>
       </c>
       <c r="P12" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2207,7 +2206,7 @@
         <v>14</v>
       </c>
       <c r="H13" s="8">
-        <v>414.2</v>
+        <v>414.7</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>57</v>
@@ -2230,7 +2229,7 @@
       </c>
       <c r="O13" s="12">
         <f t="shared" si="6"/>
-        <v>9.1743119266054496E-3</v>
+        <v>7.9575596816976457E-3</v>
       </c>
       <c r="P13" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2291,7 +2290,7 @@
         <v>133</v>
       </c>
       <c r="H14" s="8">
-        <v>158.22</v>
+        <v>158.44</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>42</v>
@@ -2308,7 +2307,7 @@
       </c>
       <c r="M14" s="11">
         <f>IFERROR(G14*H14*J14,"")</f>
-        <v>21043.26</v>
+        <v>21072.52</v>
       </c>
       <c r="N14" s="11">
         <f t="shared" si="1"/>
@@ -2316,7 +2315,7 @@
       </c>
       <c r="O14" s="12">
         <f t="shared" si="6"/>
-        <v>0.11585134622677296</v>
+        <v>0.11430194395354709</v>
       </c>
       <c r="P14" s="12">
         <f t="shared" si="2"/>
@@ -2324,11 +2323,11 @@
       </c>
       <c r="Q14" s="11">
         <f t="shared" si="3"/>
-        <v>2437.8900000000031</v>
+        <v>2408.630000000001</v>
       </c>
       <c r="R14" s="12">
         <f t="shared" si="4"/>
-        <v>0.11585134622677296</v>
+        <v>0.11430194395354709</v>
       </c>
       <c r="S14" s="12">
         <f t="shared" ca="1" si="5"/>
@@ -2377,7 +2376,7 @@
         <v>27</v>
       </c>
       <c r="H15" s="8">
-        <v>57.93</v>
+        <v>58.2</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>57</v>
@@ -2400,7 +2399,7 @@
       </c>
       <c r="O15" s="12">
         <f t="shared" si="6"/>
-        <v>1.2083549110997183E-3</v>
+        <v>-3.4364261168385868E-3</v>
       </c>
       <c r="P15" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2463,7 +2462,7 @@
         <v>39</v>
       </c>
       <c r="H16" s="8">
-        <v>46.039000000000001</v>
+        <v>46.25</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>48</v>
@@ -2486,7 +2485,7 @@
       </c>
       <c r="O16" s="12">
         <f t="shared" si="6"/>
-        <v>4.2594322205086854E-2</v>
+        <v>3.7837837837837895E-2</v>
       </c>
       <c r="P16" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2547,7 +2546,7 @@
         <v>52</v>
       </c>
       <c r="H17" s="8">
-        <v>28.96</v>
+        <v>29.05</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>48</v>
@@ -2570,7 +2569,7 @@
       </c>
       <c r="O17" s="12">
         <f>IFERROR(K17/H17-1,"")</f>
-        <v>-0.20580110497237569</v>
+        <v>-0.20826161790017217</v>
       </c>
       <c r="P17" s="12" t="str">
         <f ca="1">IFERROR(L17/J17-1,"")</f>
@@ -2631,7 +2630,7 @@
         <v>17</v>
       </c>
       <c r="H18" s="8">
-        <v>78.83</v>
+        <v>79.010000000000005</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>48</v>
@@ -2645,7 +2644,7 @@
       <c r="N18" s="11"/>
       <c r="O18" s="12">
         <f t="shared" si="6"/>
-        <v>2.1565393885576434E-3</v>
+        <v>-1.2656625743578953E-4</v>
       </c>
       <c r="P18" s="12"/>
       <c r="Q18" s="11"/>
@@ -2694,7 +2693,7 @@
         <v>185</v>
       </c>
       <c r="H19" s="8">
-        <v>10.622</v>
+        <v>10.71</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>48</v>
@@ -2717,7 +2716,7 @@
       </c>
       <c r="O19" s="12">
         <f t="shared" si="6"/>
-        <v>-0.12445867068348704</v>
+        <v>-0.13165266106442575</v>
       </c>
       <c r="P19" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2778,7 +2777,7 @@
         <v>363</v>
       </c>
       <c r="H20" s="8">
-        <v>9.9689999999999994</v>
+        <v>10</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>48</v>
@@ -2801,7 +2800,7 @@
       </c>
       <c r="O20" s="12">
         <f t="shared" si="6"/>
-        <v>0.70528638780218689</v>
+        <v>0.7</v>
       </c>
       <c r="P20" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2862,7 +2861,7 @@
         <v>9</v>
       </c>
       <c r="H21" s="8">
-        <v>108.26</v>
+        <v>108.73</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>48</v>
@@ -2885,7 +2884,7 @@
       </c>
       <c r="O21" s="12">
         <f t="shared" si="6"/>
-        <v>-3.0112691668206182E-2</v>
+        <v>-3.4305159569576027E-2</v>
       </c>
       <c r="P21" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3030,7 +3029,7 @@
         <v>44</v>
       </c>
       <c r="H23" s="8">
-        <v>56.9</v>
+        <v>57.12</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>48</v>
@@ -3053,7 +3052,7 @@
       </c>
       <c r="O23" s="12">
         <f t="shared" si="6"/>
-        <v>-1.5817223198594021E-2</v>
+        <v>-1.9607843137254832E-2</v>
       </c>
       <c r="P23" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3114,7 +3113,7 @@
         <v>47</v>
       </c>
       <c r="H24" s="8">
-        <v>27.972000000000001</v>
+        <v>28.1</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>48</v>
@@ -3137,7 +3136,7 @@
       </c>
       <c r="O24" s="12">
         <f t="shared" si="6"/>
-        <v>-7.049907049907056E-2</v>
+        <v>-7.4733096085409345E-2</v>
       </c>
       <c r="P24" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3198,7 +3197,7 @@
         <v>161</v>
       </c>
       <c r="H25" s="8">
-        <v>16.594000000000001</v>
+        <v>16.68</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>48</v>
@@ -3221,7 +3220,7 @@
       </c>
       <c r="O25" s="12">
         <f t="shared" si="6"/>
-        <v>-0.27684705315174163</v>
+        <v>-0.28057553956834536</v>
       </c>
       <c r="P25" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3282,7 +3281,7 @@
         <v>26</v>
       </c>
       <c r="H26" s="8">
-        <v>56.86</v>
+        <v>57.13</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>48</v>
@@ -3305,7 +3304,7 @@
       </c>
       <c r="O26" s="12">
         <f t="shared" si="6"/>
-        <v>-5.0298979950756273E-2</v>
+        <v>-5.4787327148608456E-2</v>
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3366,7 +3365,7 @@
         <v>15</v>
       </c>
       <c r="H27" s="8">
-        <v>95.08</v>
+        <v>95.51</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>48</v>
@@ -3389,7 +3388,7 @@
       </c>
       <c r="O27" s="12">
         <f t="shared" si="6"/>
-        <v>-0.2111905763567522</v>
+        <v>-0.214741911841692</v>
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4896,14 +4895,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>80629</v>
+        <v>74650</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>80629</v>
+        <v>74650</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>

--- a/data/AI_portfolio.xlsx
+++ b/data/AI_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\Documents\Investering\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98676285-BA67-4D03-87F5-5A0110A434F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71B4219-4AEA-4078-BC68-4177A3864DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="750" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1618,10 +1618,10 @@
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="7">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="H6" s="8">
-        <v>42.62</v>
+        <v>45.14</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>57</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="O6" s="12">
         <f t="shared" si="6"/>
-        <v>-6.1473486625997165E-2</v>
+        <v>-0.11386796632698271</v>
       </c>
       <c r="P6" s="12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4895,14 +4895,14 @@
         <v>42</v>
       </c>
       <c r="C2" s="4">
-        <v>74650</v>
+        <v>63241</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4">
         <f>C2*D2</f>
-        <v>74650</v>
+        <v>63241</v>
       </c>
       <c r="F2" s="1" t="b">
         <v>1</v>
